--- a/output/yearly_surface_area_iteration_75_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_75_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497631644871</v>
+        <v>10.84497634382119</v>
       </c>
       <c r="C21" t="n">
-        <v>37.789071886972</v>
+        <v>37.7890719823508</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.42357522888688</v>
+        <v>5.133558745506572</v>
       </c>
       <c r="C2" t="n">
-        <v>7.955101647511905</v>
+        <v>8.408669086873932</v>
       </c>
       <c r="D2" t="n">
-        <v>28.62776305583699</v>
+        <v>41.90491900807086</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.2709466708389</v>
+        <v>16.69461971071701</v>
       </c>
       <c r="C3" t="n">
-        <v>28.27433388230814</v>
+        <v>22.90908267859932</v>
       </c>
       <c r="D3" t="n">
-        <v>49.97586688468388</v>
+        <v>86.94357668809754</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.2145704455361</v>
+        <v>35.63351467334223</v>
       </c>
       <c r="C4" t="n">
-        <v>64.09438061945727</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D4" t="n">
-        <v>65.45999167606458</v>
+        <v>105.1520513587631</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.06346341454012</v>
+        <v>43.71231653158924</v>
       </c>
       <c r="C5" t="n">
-        <v>87.25282721493528</v>
+        <v>96.13764393836894</v>
       </c>
       <c r="D5" t="n">
-        <v>50.19185137961819</v>
+        <v>75.49639845657973</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.36740429222912</v>
+        <v>40.6139207769863</v>
       </c>
       <c r="C6" t="n">
-        <v>91.00899393138359</v>
+        <v>111.6178417389326</v>
       </c>
       <c r="D6" t="n">
-        <v>38.76234460677682</v>
+        <v>49.14727182229959</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.08788393395925</v>
+        <v>28.86534600026472</v>
       </c>
       <c r="C7" t="n">
-        <v>76.05599464800039</v>
+        <v>80.30794395509334</v>
       </c>
       <c r="D7" t="n">
-        <v>38.14777054391831</v>
+        <v>39.34550274309942</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.77730750205199</v>
+        <v>15.0207398749762</v>
       </c>
       <c r="C8" t="n">
-        <v>48.06636759992384</v>
+        <v>45.72980806381643</v>
       </c>
       <c r="D8" t="n">
-        <v>36.21667280966483</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>33.17030968338697</v>
+        <v>30.61874740004951</v>
       </c>
       <c r="D9" t="n">
         <v>34.27968458918587</v>
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.694136684631501</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>29.18245050873644</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>30.20837685967435</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>28.42257778564941</v>
+        <v>27.98864530037232</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>26.27647730416588</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -954,7 +954,7 @@
         <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.730277981556361</v>
+        <v>7.706592246426005</v>
       </c>
       <c r="C21" t="n">
-        <v>96.62847476945451</v>
+        <v>95.36907904952182</v>
       </c>
       <c r="D21" t="n">
-        <v>8.696562729250905</v>
+        <v>8.669916277229255</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.037568454668637</v>
+        <v>6.043638867343365</v>
       </c>
       <c r="C2" t="n">
-        <v>12.67141761871358</v>
+        <v>8.501935118777377</v>
       </c>
       <c r="D2" t="n">
-        <v>27.49089921431919</v>
+        <v>33.96061658530567</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.92733497435251</v>
+        <v>16.87133429748144</v>
       </c>
       <c r="C3" t="n">
-        <v>29.57514959043516</v>
+        <v>27.92581344730052</v>
       </c>
       <c r="D3" t="n">
-        <v>59.95042355983148</v>
+        <v>97.76734512741861</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.0614178036736</v>
+        <v>33.43832680664636</v>
       </c>
       <c r="C4" t="n">
-        <v>66.83836545282711</v>
+        <v>56.6664774891259</v>
       </c>
       <c r="D4" t="n">
-        <v>74.6108620273491</v>
+        <v>120.6715190674967</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.65942532874693</v>
+        <v>48.15472489330606</v>
       </c>
       <c r="C5" t="n">
-        <v>103.0589652533089</v>
+        <v>98.81290643244149</v>
       </c>
       <c r="D5" t="n">
-        <v>60.52474596681587</v>
+        <v>93.87962421860125</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>61.98755004614362</v>
+        <v>49.75104666041137</v>
       </c>
       <c r="C6" t="n">
-        <v>113.6706761885127</v>
+        <v>131.7034180201181</v>
       </c>
       <c r="D6" t="n">
-        <v>45.32336451425826</v>
+        <v>59.4516957260741</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>50.60418541540184</v>
+        <v>37.96811071404115</v>
       </c>
       <c r="C7" t="n">
-        <v>103.9032682789612</v>
+        <v>118.0963948392573</v>
       </c>
       <c r="D7" t="n">
-        <v>40.42346172236242</v>
+        <v>44.19631814978291</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>30.12492830481337</v>
+        <v>22.61455836732527</v>
       </c>
       <c r="C8" t="n">
-        <v>73.60162538738336</v>
+        <v>74.85335371029805</v>
       </c>
       <c r="D8" t="n">
-        <v>38.46978379091126</v>
+        <v>38.21943812632832</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.19999879422586</v>
+        <v>11.31562403914873</v>
       </c>
       <c r="C9" t="n">
-        <v>46.70468353413349</v>
+        <v>42.93280885441725</v>
       </c>
       <c r="D9" t="n">
-        <v>35.61093447614454</v>
+        <v>35.94374694788421</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.975317438673588</v>
+        <v>6.548257187326225</v>
       </c>
       <c r="C10" t="n">
-        <v>35.01894061048373</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>31.98534020436108</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>37.13853390395258</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>31.67707142522758</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.87810872041993</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.42668470291564</v>
+        <v>26.11939767148639</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.921779249433463</v>
+        <v>7.890844756452964</v>
       </c>
       <c r="C21" t="n">
-        <v>105.9537974611726</v>
+        <v>104.5536930230018</v>
       </c>
       <c r="D21" t="n">
-        <v>9.902224061791829</v>
+        <v>9.863555945566205</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.916633560597031</v>
+        <v>9.082148011987242</v>
       </c>
       <c r="C2" t="n">
-        <v>11.07509585160827</v>
+        <v>9.200939484201108</v>
       </c>
       <c r="D2" t="n">
-        <v>28.10841852029043</v>
+        <v>39.2591089451257</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.06754496961056</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C3" t="n">
-        <v>39.08828484458675</v>
+        <v>30.18874190558942</v>
       </c>
       <c r="D3" t="n">
-        <v>65.93417581721579</v>
+        <v>100.5702348230433</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.79790850830795</v>
+        <v>32.23863111205676</v>
       </c>
       <c r="C4" t="n">
-        <v>69.42919764433444</v>
+        <v>62.67771868222911</v>
       </c>
       <c r="D4" t="n">
-        <v>84.10632582282423</v>
+        <v>137.5055469522167</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>61.6537558266997</v>
+        <v>49.2837347531899</v>
       </c>
       <c r="C5" t="n">
-        <v>112.4101121362598</v>
+        <v>100.187353218387</v>
       </c>
       <c r="D5" t="n">
-        <v>71.42214548395546</v>
+        <v>110.0048302608551</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>69.51460969460392</v>
+        <v>56.11080828852221</v>
       </c>
       <c r="C6" t="n">
-        <v>135.366318704663</v>
+        <v>143.2958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>52.04539104523617</v>
+        <v>72.25172229404403</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>61.02445554827749</v>
+        <v>47.07087542781757</v>
       </c>
       <c r="C7" t="n">
-        <v>131.9302017397991</v>
+        <v>148.8781123582118</v>
       </c>
       <c r="D7" t="n">
-        <v>43.95677170994669</v>
+        <v>49.34656660626167</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>41.14013754646259</v>
+        <v>30.54217107911827</v>
       </c>
       <c r="C8" t="n">
-        <v>102.1410311498382</v>
+        <v>110.0686438616311</v>
       </c>
       <c r="D8" t="n">
-        <v>40.13875488813084</v>
+        <v>40.97324043674063</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21.41093568191868</v>
+        <v>16.30781111524376</v>
       </c>
       <c r="C9" t="n">
-        <v>67.22811929141305</v>
+        <v>65.00936947981526</v>
       </c>
       <c r="D9" t="n">
-        <v>37.27499683484289</v>
+        <v>37.05312185368311</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.82238578098934</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>44.12955930589413</v>
+        <v>40.9977841293468</v>
       </c>
       <c r="D10" t="n">
-        <v>36.72718161587318</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.686282702997524</v>
+        <v>5.508586368528851</v>
       </c>
       <c r="C11" t="n">
-        <v>36.60544490054656</v>
+        <v>35.36157055926586</v>
       </c>
       <c r="D11" t="n">
         <v>37.13853390395258</v>
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.339324852770901</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>36.01639627799849</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.382120841130262</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>31.47974013667398</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>34.08137155292803</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>28.88498095434966</v>
+        <v>28.27040689149115</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.44199175555609</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>22.7323680918349</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>20.30548776693678</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>19.26188995732242</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.097412847633777</v>
+        <v>8.060122198478259</v>
       </c>
       <c r="C21" t="n">
-        <v>114.3759564728271</v>
+        <v>112.8417107786956</v>
       </c>
       <c r="D21" t="n">
-        <v>11.13394266549644</v>
+        <v>11.0826680229076</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.930958865533233</v>
+        <v>8.049349427119598</v>
       </c>
       <c r="C2" t="n">
-        <v>7.35329030480861</v>
+        <v>6.182065293642165</v>
       </c>
       <c r="D2" t="n">
-        <v>22.76771100918778</v>
+        <v>32.1787445020977</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.28062527916112</v>
+        <v>22.18749811597792</v>
       </c>
       <c r="C3" t="n">
-        <v>55.30675691874407</v>
+        <v>44.5860719883689</v>
       </c>
       <c r="D3" t="n">
-        <v>71.5154115158589</v>
+        <v>108.4242164570177</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.62227348023901</v>
+        <v>23.67484588791183</v>
       </c>
       <c r="C4" t="n">
-        <v>96.10328276872026</v>
+        <v>84.91037719260238</v>
       </c>
       <c r="D4" t="n">
-        <v>81.01774754526377</v>
+        <v>130.0648811017302</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.14718970684157</v>
+        <v>31.6122760767473</v>
       </c>
       <c r="C5" t="n">
-        <v>80.87146713733101</v>
+        <v>85.60839981032187</v>
       </c>
       <c r="D5" t="n">
-        <v>50.97724954301564</v>
+        <v>73.77833997414781</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.8768081775462</v>
+        <v>29.22270216461057</v>
       </c>
       <c r="C6" t="n">
-        <v>86.86307337634931</v>
+        <v>98.05303370935445</v>
       </c>
       <c r="D6" t="n">
-        <v>28.94094057349173</v>
+        <v>32.48308629041422</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.24840753137022</v>
+        <v>20.24167416616073</v>
       </c>
       <c r="C7" t="n">
-        <v>71.80404534090746</v>
+        <v>77.37350006709961</v>
       </c>
       <c r="D7" t="n">
-        <v>28.20659329071511</v>
+        <v>28.80545939030566</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.85384276525424</v>
+        <v>11.26555490623215</v>
       </c>
       <c r="C8" t="n">
-        <v>49.48499303256047</v>
+        <v>47.89947049020188</v>
       </c>
       <c r="D8" t="n">
-        <v>27.45457454926205</v>
+        <v>27.28767743954009</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.989061906533041</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>33.61405964570653</v>
+        <v>31.28437234352885</v>
       </c>
       <c r="D9" t="n">
-        <v>27.95624762613216</v>
+        <v>27.73437264497238</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.128249096357838</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>28.61303684027329</v>
+        <v>27.75891633757857</v>
       </c>
       <c r="D10" t="n">
         <v>29.04009709162065</v>
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.198534020436107</v>
+        <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>28.78680618392497</v>
+        <v>28.60910984945629</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.603594911662541</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>27.77167905773377</v>
+        <v>26.90381408717959</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.505641125416113</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C2" t="n">
-        <v>3.868085954732433</v>
+        <v>3.385066084243002</v>
       </c>
       <c r="D2" t="n">
-        <v>17.21690948937631</v>
+        <v>22.33574201931918</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.96923133046564</v>
+        <v>25.4861704022472</v>
       </c>
       <c r="C3" t="n">
-        <v>42.13170272775187</v>
+        <v>34.68514639103981</v>
       </c>
       <c r="D3" t="n">
-        <v>74.05813806985815</v>
+        <v>109.3126981293611</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.77238306799753</v>
+        <v>32.12376663065989</v>
       </c>
       <c r="C4" t="n">
-        <v>119.7653659364769</v>
+        <v>100.9914045881651</v>
       </c>
       <c r="D4" t="n">
-        <v>95.43962132064942</v>
+        <v>151.9274207276024</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.83503499462009</v>
+        <v>35.19565519724816</v>
       </c>
       <c r="C5" t="n">
-        <v>127.9708132485718</v>
+        <v>119.1596276029566</v>
       </c>
       <c r="D5" t="n">
-        <v>64.96715432853269</v>
+        <v>94.95954669327274</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.56487444950297</v>
+        <v>35.05919226635785</v>
       </c>
       <c r="C6" t="n">
-        <v>108.8002258277443</v>
+        <v>119.0241464197706</v>
       </c>
       <c r="D6" t="n">
-        <v>34.65667570761666</v>
+        <v>41.49945720621693</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.81112889235289</v>
+        <v>19.10382857693868</v>
       </c>
       <c r="C7" t="n">
-        <v>93.72254458592174</v>
+        <v>102.9450825196163</v>
       </c>
       <c r="D7" t="n">
-        <v>30.42239785920016</v>
+        <v>31.50035683846316</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.2669375645639</v>
+        <v>9.429686699290613</v>
       </c>
       <c r="C8" t="n">
-        <v>66.17470400475625</v>
+        <v>64.58918146239766</v>
       </c>
       <c r="D8" t="n">
-        <v>28.70630287217673</v>
+        <v>28.45595720759379</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.435937038414587</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>40.04843409934012</v>
+        <v>36.94218436310322</v>
       </c>
       <c r="D9" t="n">
-        <v>29.17656002251095</v>
+        <v>28.73281006019139</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.2776546738526</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.954659679155399</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>30.74146586308036</v>
+        <v>30.03068052520567</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.43093048890212</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.67163860289184</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.69185439405351</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.613052535806514</v>
+        <v>4.667228585989336</v>
       </c>
       <c r="C2" t="n">
-        <v>7.256097282088176</v>
+        <v>6.787803627162447</v>
       </c>
       <c r="D2" t="n">
-        <v>21.57096055771092</v>
+        <v>27.04616750429538</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.72531593145592</v>
+        <v>20.63142800474672</v>
       </c>
       <c r="C3" t="n">
-        <v>27.36130851735861</v>
+        <v>23.0219836645877</v>
       </c>
       <c r="D3" t="n">
-        <v>70.69074344429158</v>
+        <v>103.1816837163398</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.8466770983508</v>
+        <v>40.40677201139022</v>
       </c>
       <c r="C4" t="n">
-        <v>112.0694456828861</v>
+        <v>93.48692513690251</v>
       </c>
       <c r="D4" t="n">
-        <v>109.3126981293611</v>
+        <v>167.4341257161808</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.89165756629692</v>
+        <v>41.33157834879072</v>
       </c>
       <c r="C5" t="n">
-        <v>176.6409556866074</v>
+        <v>153.8398652554752</v>
       </c>
       <c r="D5" t="n">
-        <v>82.31954500109507</v>
+        <v>124.2401719724339</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.327152636355</v>
+        <v>40.89568236810514</v>
       </c>
       <c r="C6" t="n">
-        <v>154.284596965499</v>
+        <v>152.3122658276672</v>
       </c>
       <c r="D6" t="n">
-        <v>45.2026095466359</v>
+        <v>58.48565598509524</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.96811071404115</v>
+        <v>28.38625312059227</v>
       </c>
       <c r="C7" t="n">
-        <v>125.282788034344</v>
+        <v>136.6013573166054</v>
       </c>
       <c r="D7" t="n">
-        <v>33.17718191731671</v>
+        <v>35.93196597543326</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.27523351455438</v>
+        <v>13.60211444233956</v>
       </c>
       <c r="C8" t="n">
-        <v>93.87962421860124</v>
+        <v>97.63480918734528</v>
       </c>
       <c r="D8" t="n">
-        <v>30.54217107911827</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.876561831172157</v>
+        <v>6.434374453633594</v>
       </c>
       <c r="C9" t="n">
-        <v>59.57343244140068</v>
+        <v>56.24530772400399</v>
       </c>
       <c r="D9" t="n">
-        <v>29.84218496599028</v>
+        <v>29.50937249425062</v>
       </c>
     </row>
     <row r="10">
@@ -2447,10 +2447,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.131775176547325</v>
+        <v>2.847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>38.86248287260999</v>
+        <v>36.72718161587318</v>
       </c>
       <c r="D10" t="n">
         <v>30.7483380970101</v>
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.954659679155399</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>34.47308888692249</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>30.56376952861169</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>26.68684784454105</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.03256190515617</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.902447124381071</v>
+        <v>2.770492021384499</v>
       </c>
       <c r="C2" t="n">
-        <v>3.272165098254619</v>
+        <v>3.111158474758142</v>
       </c>
       <c r="D2" t="n">
-        <v>14.85187926984575</v>
+        <v>18.66596910084461</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.83959957577605</v>
+        <v>20.52834449580081</v>
       </c>
       <c r="C3" t="n">
-        <v>29.5800583289564</v>
+        <v>26.03594911662541</v>
       </c>
       <c r="D3" t="n">
-        <v>73.15493018195109</v>
+        <v>104.2910586221387</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>56.36017220540089</v>
+        <v>44.78438502462675</v>
       </c>
       <c r="C4" t="n">
-        <v>107.4238155463902</v>
+        <v>90.10480429577225</v>
       </c>
       <c r="D4" t="n">
-        <v>118.3742294395592</v>
+        <v>182.2771692566883</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.78781329382501</v>
+        <v>43.44233591292137</v>
       </c>
       <c r="C5" t="n">
-        <v>208.9649988489336</v>
+        <v>181.3288009743859</v>
       </c>
       <c r="D5" t="n">
-        <v>89.78082755337083</v>
+        <v>131.1860369799801</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.32336451425826</v>
+        <v>34.25415914887547</v>
       </c>
       <c r="C6" t="n">
-        <v>190.1890740052134</v>
+        <v>185.1173653650744</v>
       </c>
       <c r="D6" t="n">
-        <v>45.08185457901354</v>
+        <v>56.91584140600459</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.0970952117292</v>
+        <v>8.982991493858314</v>
       </c>
       <c r="C7" t="n">
-        <v>129.594623951396</v>
+        <v>137.6793162958684</v>
       </c>
       <c r="D7" t="n">
-        <v>33.89582123682538</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>73.35127972280043</v>
+        <v>72.01610284502478</v>
       </c>
       <c r="D8" t="n">
-        <v>32.21114217633784</v>
+        <v>31.71045084717197</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>29.62030998483051</v>
+        <v>27.95624762613216</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
-        <v>23.91537407545231</v>
+        <v>23.48831382410494</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>21.32356013624072</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.806055922915637</v>
+        <v>3.454770171244526</v>
       </c>
       <c r="C2" t="n">
-        <v>9.36292785540183</v>
+        <v>5.637195317785186</v>
       </c>
       <c r="D2" t="n">
-        <v>13.37336722725005</v>
+        <v>22.89730170614836</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.7625812864883</v>
+        <v>15.21218067730433</v>
       </c>
       <c r="C3" t="n">
-        <v>20.87195619228719</v>
+        <v>18.96736564604837</v>
       </c>
       <c r="D3" t="n">
-        <v>68.3885450778328</v>
+        <v>95.78912350336128</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>53.14396672628834</v>
+        <v>42.14250195249858</v>
       </c>
       <c r="C4" t="n">
-        <v>90.53873678104935</v>
+        <v>77.68667758475436</v>
       </c>
       <c r="D4" t="n">
-        <v>126.4913194582718</v>
+        <v>192.9850914669082</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>68.69779560467057</v>
+        <v>53.70159942230054</v>
       </c>
       <c r="C5" t="n">
-        <v>205.5043381914636</v>
+        <v>175.6592079823606</v>
       </c>
       <c r="D5" t="n">
-        <v>108.2131407006047</v>
+        <v>158.7731474693154</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.04288777047993</v>
+        <v>44.1560664939088</v>
       </c>
       <c r="C6" t="n">
-        <v>256.1212863270207</v>
+        <v>232.6143192965351</v>
       </c>
       <c r="D6" t="n">
-        <v>59.61270234957058</v>
+        <v>77.40393424593128</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.11056194214817</v>
+        <v>19.16371518689774</v>
       </c>
       <c r="C7" t="n">
-        <v>195.1704618565616</v>
+        <v>195.6495547362341</v>
       </c>
       <c r="D7" t="n">
-        <v>37.72856427420492</v>
+        <v>41.86074036137975</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.593818492349078</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>114.658314378985</v>
+        <v>116.8279768053704</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>33.62976760897448</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.884374755077128</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>53.0281204971872</v>
+        <v>50.58749570442963</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.565887588273662</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>25.05518316008284</v>
+        <v>23.98900515327081</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.65909686691488</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>14.13520344574558</v>
+      </c>
+      <c r="D14" t="n">
         <v>14.44249047717483</v>
-      </c>
-      <c r="D14" t="n">
-        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.890666151930109</v>
+        <v>2.359139733305085</v>
       </c>
       <c r="C2" t="n">
-        <v>4.851797154387737</v>
+        <v>2.97960428238907</v>
       </c>
       <c r="D2" t="n">
-        <v>10.04229726674062</v>
+        <v>16.66418553188536</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.97856578142259</v>
+        <v>13.90645623065607</v>
       </c>
       <c r="C3" t="n">
-        <v>28.64739800992193</v>
+        <v>20.70505908256523</v>
       </c>
       <c r="D3" t="n">
-        <v>64.4811892149305</v>
+        <v>92.81933669801469</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.43452298901639</v>
+        <v>37.75212621910685</v>
       </c>
       <c r="C4" t="n">
-        <v>76.28277836768142</v>
+        <v>66.11089040398021</v>
       </c>
       <c r="D4" t="n">
-        <v>130.7540679901115</v>
+        <v>196.4948395095906</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>75.25096153051803</v>
+        <v>59.02758071783948</v>
       </c>
       <c r="C5" t="n">
-        <v>195.6868611489955</v>
+        <v>169.1551294417254</v>
       </c>
       <c r="D5" t="n">
-        <v>122.5466571826081</v>
+        <v>181.4515194374167</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>67.74353683614267</v>
+        <v>51.88438442173969</v>
       </c>
       <c r="C6" t="n">
-        <v>295.0043859014199</v>
+        <v>259.4621737645726</v>
       </c>
       <c r="D6" t="n">
-        <v>70.23913950033806</v>
+        <v>93.78635818669781</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.49362347325367</v>
+        <v>17.96598298771663</v>
       </c>
       <c r="C7" t="n">
-        <v>252.0627413176643</v>
+        <v>245.8345338819225</v>
       </c>
       <c r="D7" t="n">
-        <v>42.27994663109313</v>
+        <v>48.08894779712151</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.175193059712437</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>153.5453409442011</v>
+        <v>153.3784438344792</v>
       </c>
       <c r="D8" t="n">
-        <v>35.29873870619407</v>
+        <v>34.71459882216722</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>62.34686970589792</v>
+        <v>59.68436993198057</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>25.48126166372597</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.52209415667683</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.96750451476862</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.909139431861552</v>
+        <v>4.295146206079795</v>
       </c>
       <c r="C2" t="n">
-        <v>4.665265090580843</v>
+        <v>8.566730467257669</v>
       </c>
       <c r="D2" t="n">
-        <v>13.80337272171015</v>
+        <v>27.1787034443687</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.65044106402591</v>
+        <v>11.07411410390402</v>
       </c>
       <c r="C3" t="n">
-        <v>23.85646921319749</v>
+        <v>16.49336143134641</v>
       </c>
       <c r="D3" t="n">
-        <v>58.63979037466198</v>
+        <v>85.73602701187394</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.16351956491527</v>
+        <v>32.31520743298801</v>
       </c>
       <c r="C4" t="n">
-        <v>73.90891241881263</v>
+        <v>59.53808952404782</v>
       </c>
       <c r="D4" t="n">
-        <v>132.0813908862531</v>
+        <v>196.9670601553333</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>74.95643721924398</v>
+        <v>58.65942532874693</v>
       </c>
       <c r="C5" t="n">
-        <v>171.3886054688869</v>
+        <v>148.6856898081795</v>
       </c>
       <c r="D5" t="n">
-        <v>134.9657656413303</v>
+        <v>202.3136581526615</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>79.77878194250432</v>
+        <v>62.22905998138833</v>
       </c>
       <c r="C6" t="n">
-        <v>302.6522005175025</v>
+        <v>264.1716175018445</v>
       </c>
       <c r="D6" t="n">
-        <v>86.86307337634931</v>
+        <v>118.0178550229176</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>43.71722527011047</v>
+        <v>32.39865598784899</v>
       </c>
       <c r="C7" t="n">
-        <v>325.8430447872205</v>
+        <v>297.9358845463008</v>
       </c>
       <c r="D7" t="n">
-        <v>49.76577287597506</v>
+        <v>57.85046522044755</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.60073178400781</v>
+        <v>9.262789589568655</v>
       </c>
       <c r="C8" t="n">
-        <v>223.2248842531185</v>
+        <v>221.5559131558989</v>
       </c>
       <c r="D8" t="n">
-        <v>37.63529824230147</v>
+        <v>38.46978379091126</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.328124717396686</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>110.1609281458303</v>
+        <v>106.8328034284336</v>
       </c>
       <c r="D9" t="n">
-        <v>34.83437204208531</v>
+        <v>33.50312215512664</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>47.40368789955724</v>
+        <v>44.55661955724149</v>
       </c>
       <c r="D10" t="n">
-        <v>26.76244241776806</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>27.8983245115816</v>
       </c>
       <c r="D11" t="n">
-        <v>24.87748682561417</v>
+        <v>24.6997904911455</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
         <v>16.91060420565131</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.29148125717007</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>12.29148125717007</v>
+        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.049930264196345</v>
+        <v>5.245477983790708</v>
       </c>
       <c r="C2" t="n">
-        <v>3.524474258246049</v>
+        <v>2.951133598965912</v>
       </c>
       <c r="D2" t="n">
-        <v>4.106650646864408</v>
+        <v>5.219952543480291</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.228387362191013</v>
+        <v>3.070906818884023</v>
       </c>
       <c r="C2" t="n">
-        <v>2.649737053762141</v>
+        <v>4.934263961544469</v>
       </c>
       <c r="D2" t="n">
-        <v>10.16010699125024</v>
+        <v>20.00310947402876</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.01569226773472</v>
+        <v>15.34471661737765</v>
       </c>
       <c r="C3" t="n">
-        <v>25.79051219056371</v>
+        <v>23.84174299763379</v>
       </c>
       <c r="D3" t="n">
-        <v>64.12285130288042</v>
+        <v>96.0934652916778</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>58.09590214650925</v>
+        <v>44.4015034199705</v>
       </c>
       <c r="C4" t="n">
-        <v>104.8712715153485</v>
+        <v>85.76547944300135</v>
       </c>
       <c r="D4" t="n">
-        <v>134.7615621188469</v>
+        <v>201.0894187654657</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.02571503342222</v>
+        <v>36.66827675361837</v>
       </c>
       <c r="C5" t="n">
-        <v>256.5552188122978</v>
+        <v>221.8995248523854</v>
       </c>
       <c r="D5" t="n">
-        <v>123.11116211255</v>
+        <v>180.911558200081</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.12961605915636</v>
+        <v>20.0855762811855</v>
       </c>
       <c r="C6" t="n">
-        <v>273.9125182233814</v>
+        <v>247.9904518404486</v>
       </c>
       <c r="D6" t="n">
-        <v>71.04417261782045</v>
+        <v>90.96874227550947</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.324238784308704</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>156.9628047026843</v>
+        <v>155.7650725035032</v>
       </c>
       <c r="D7" t="n">
-        <v>32.75797564760332</v>
+        <v>34.37491411649782</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.253110981246429</v>
+        <v>1.835868206941535</v>
       </c>
       <c r="C8" t="n">
-        <v>81.19544387973245</v>
+        <v>78.69198723390308</v>
       </c>
       <c r="D8" t="n">
-        <v>25.61870634232051</v>
+        <v>24.61732368398877</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>36.16562192904399</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>20.41249826669968</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.91890015564179</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>19.50241814486289</v>
+        <v>19.3600647277471</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>17.05884810899257</v>
+        <v>16.52575910558656</v>
       </c>
       <c r="D11" t="n">
-        <v>16.52575910558656</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.28224461720434</v>
+        <v>11.0652783745658</v>
       </c>
       <c r="D12" t="n">
         <v>13.66887328622834</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.14636252339079</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>10.14636252339079</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.246680715673207</v>
+        <v>6.501133297522379</v>
       </c>
       <c r="C2" t="n">
-        <v>3.566689409528662</v>
+        <v>3.376230354904781</v>
       </c>
       <c r="D2" t="n">
-        <v>6.068182559949535</v>
+        <v>19.80086944695392</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.97165248976386</v>
+        <v>11.14774518172253</v>
       </c>
       <c r="C3" t="n">
-        <v>9.022261402028187</v>
+        <v>7.554548584179206</v>
       </c>
       <c r="D3" t="n">
-        <v>6.74951546669682</v>
+        <v>7.731263170943632</v>
       </c>
     </row>
     <row r="4">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39948418306575</v>
+        <v>13.39970210993115</v>
       </c>
       <c r="C21" t="n">
-        <v>70.15024072310892</v>
+        <v>70.15138163434543</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576409903890088</v>
+        <v>1.576435542344841</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.412375093512666</v>
+        <v>4.444371857125311</v>
       </c>
       <c r="C2" t="n">
-        <v>3.992767913171777</v>
+        <v>6.481498343437441</v>
       </c>
       <c r="D2" t="n">
-        <v>11.42361628661589</v>
+        <v>24.0685267173148</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.39995653072273</v>
+        <v>17.91198686398306</v>
       </c>
       <c r="C3" t="n">
-        <v>12.13440162449058</v>
+        <v>11.1281102276376</v>
       </c>
       <c r="D3" t="n">
-        <v>10.21508486268806</v>
+        <v>22.49183990429443</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>17.33177397077319</v>
+        <v>13.01797455831271</v>
       </c>
       <c r="C4" t="n">
-        <v>14.5112128164721</v>
+        <v>12.23944862884498</v>
       </c>
       <c r="D4" t="n">
-        <v>18.60804598629404</v>
+        <v>19.11855479250239</v>
       </c>
     </row>
     <row r="5">
@@ -4907,10 +4907,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>25.36836067773758</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
         <v>36.80081269369168</v>
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.84843530511426</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4994,7 +4994,7 @@
         <v>4.302018440009523</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5008,7 +5008,7 @@
         <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
-        <v>26.87534340375643</v>
+        <v>26.51700549170635</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44670863604736</v>
+        <v>15.4455230581666</v>
       </c>
       <c r="C21" t="n">
-        <v>86.17637449584318</v>
+        <v>86.16976021924525</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251938660220497</v>
+        <v>3.251689064877179</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.21740821099505</v>
+        <v>4.896957548783091</v>
       </c>
       <c r="C2" t="n">
-        <v>7.098035901704439</v>
+        <v>8.095491569219199</v>
       </c>
       <c r="D2" t="n">
-        <v>22.32199755145973</v>
+        <v>35.57657330649591</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.78850763742621</v>
+        <v>16.67007601811084</v>
       </c>
       <c r="C3" t="n">
-        <v>14.24025045009999</v>
+        <v>19.67422399310608</v>
       </c>
       <c r="D3" t="n">
-        <v>16.97932654494859</v>
+        <v>36.52592333650258</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.59147944850886</v>
+        <v>25.20637230653686</v>
       </c>
       <c r="C4" t="n">
-        <v>24.01943933210246</v>
+        <v>21.31374265919825</v>
       </c>
       <c r="D4" t="n">
-        <v>19.38657191576176</v>
+        <v>26.08699999724625</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>15.11891464540088</v>
+        <v>11.75642875835556</v>
       </c>
       <c r="C5" t="n">
-        <v>17.81872083207961</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="D5" t="n">
-        <v>29.50151851261666</v>
+        <v>29.32971266437347</v>
       </c>
     </row>
     <row r="6">
@@ -5190,7 +5190,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.876741757621407</v>
       </c>
       <c r="C6" t="n">
         <v>12.19625172985813</v>
@@ -5204,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
         <v>37.42913122440964</v>
@@ -5218,10 +5218,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.51451791248334</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.6242369756475</v>
       </c>
       <c r="D8" t="n">
         <v>38.55323234577224</v>
@@ -5238,7 +5238,7 @@
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>40.82499653339935</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5249,10 @@
         <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.82369599052563</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5277,7 +5277,7 @@
         <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>31.67707142522758</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
         <v>45.77987719673301</v>
@@ -5291,7 +5291,7 @@
         <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5319,7 +5319,7 @@
         <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.95035713990669</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
         <v>43.35888735806038</v>
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5347,7 +5347,7 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74815989656564</v>
+        <v>16.74414977476293</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1637753690504</v>
+        <v>102.1393136260539</v>
       </c>
       <c r="D21" t="n">
-        <v>5.024447968969691</v>
+        <v>5.023244932428881</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.744205817548087</v>
+        <v>5.531166565726529</v>
       </c>
       <c r="C2" t="n">
-        <v>4.347178834404876</v>
+        <v>7.170685231818704</v>
       </c>
       <c r="D2" t="n">
-        <v>22.02649149248144</v>
+        <v>26.66328589963912</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.32356013624072</v>
+        <v>16.72898088036565</v>
       </c>
       <c r="C3" t="n">
-        <v>22.05987091442583</v>
+        <v>26.57591035396116</v>
       </c>
       <c r="D3" t="n">
-        <v>30.16419821298325</v>
+        <v>55.43929285881739</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.088464771036</v>
+        <v>28.94584931201296</v>
       </c>
       <c r="C4" t="n">
-        <v>30.63052837250048</v>
+        <v>37.19056653227767</v>
       </c>
       <c r="D4" t="n">
-        <v>23.12604892123787</v>
+        <v>37.59897357724434</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.98672286269284</v>
+        <v>25.05911015089984</v>
       </c>
       <c r="C5" t="n">
-        <v>32.25041208450773</v>
+        <v>28.56885819358219</v>
       </c>
       <c r="D5" t="n">
-        <v>30.01693605734623</v>
+        <v>32.22586839190156</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.4038014060817</v>
+        <v>10.90819874188631</v>
       </c>
       <c r="C6" t="n">
-        <v>20.85035774279376</v>
+        <v>18.55601335796896</v>
       </c>
       <c r="D6" t="n">
-        <v>37.75605320992383</v>
+        <v>38.07806645691679</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.08008670558751</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.79389940203295</v>
       </c>
       <c r="D8" t="n">
         <v>40.38910055271378</v>
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.87187407682917</v>
       </c>
       <c r="C9" t="n">
-        <v>34.50155957034565</v>
+        <v>34.16874709860598</v>
       </c>
       <c r="D9" t="n">
-        <v>41.60155896745857</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5588,7 +5588,7 @@
         <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.71459882216721</v>
       </c>
       <c r="D12" t="n">
         <v>47.29864089520282</v>
@@ -5602,7 +5602,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5613,7 +5613,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="C14" t="n">
         <v>30.72870314292517</v>
@@ -5686,7 +5686,7 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>37.91411459030757</v>
       </c>
       <c r="D19" t="n">
         <v>25.27607639353838</v>
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.08459512231015</v>
+        <v>18.07561705803875</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9804538931662</v>
+        <v>117.9218827119671</v>
       </c>
       <c r="D21" t="n">
-        <v>6.889369570403866</v>
+        <v>6.885949355443333</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.151050277733766</v>
+        <v>5.751078051477815</v>
       </c>
       <c r="C2" t="n">
-        <v>7.65468685001238</v>
+        <v>4.848851911274997</v>
       </c>
       <c r="D2" t="n">
-        <v>17.21494599396782</v>
+        <v>27.20128364156637</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.2212373908208</v>
+        <v>16.10557108816893</v>
       </c>
       <c r="C3" t="n">
-        <v>17.91689560250429</v>
+        <v>25.70706363570273</v>
       </c>
       <c r="D3" t="n">
-        <v>37.8120128290659</v>
+        <v>59.6215380789088</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.70335762906399</v>
+        <v>22.62830283518473</v>
       </c>
       <c r="C4" t="n">
-        <v>37.19056653227767</v>
+        <v>45.18002934943821</v>
       </c>
       <c r="D4" t="n">
-        <v>28.18008610270045</v>
+        <v>48.49833658979244</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.63619787454772</v>
+        <v>21.03394456348791</v>
       </c>
       <c r="C5" t="n">
-        <v>34.09118902997049</v>
+        <v>37.35550014659114</v>
       </c>
       <c r="D5" t="n">
-        <v>25.72178985126644</v>
+        <v>31.24412068765475</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.97990738202533</v>
+        <v>12.3572583533546</v>
       </c>
       <c r="C6" t="n">
-        <v>25.15728492132452</v>
+        <v>22.29941735426205</v>
       </c>
       <c r="D6" t="n">
-        <v>29.90698031447059</v>
+        <v>30.59125846433062</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.168320825782709</v>
+        <v>5.509568116233099</v>
       </c>
       <c r="C7" t="n">
-        <v>16.5287043486993</v>
+        <v>15.63040519931347</v>
       </c>
       <c r="D7" t="n">
-        <v>31.38058361854505</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.992187076095029</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>22.18749811597791</v>
       </c>
       <c r="D9" t="n">
-        <v>30.06405994715006</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.78007281871549</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.29539255245382</v>
       </c>
     </row>
     <row r="12">
@@ -5899,7 +5899,7 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
         <v>32.32797015314322</v>
@@ -5913,7 +5913,7 @@
         <v>2.081305133003238</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
         <v>30.17892442854696</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>29.80684204863741</v>
@@ -5986,7 +5986,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.073169353761567</v>
+        <v>7.067357470264312</v>
       </c>
       <c r="C21" t="n">
-        <v>67.19510886073488</v>
+        <v>66.25647628372792</v>
       </c>
       <c r="D21" t="n">
-        <v>5.304877015321175</v>
+        <v>5.300518102698234</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.939974521320702</v>
+        <v>5.798201941281662</v>
       </c>
       <c r="C2" t="n">
-        <v>7.506442946671113</v>
+        <v>6.270422587024377</v>
       </c>
       <c r="D2" t="n">
-        <v>17.48001787411446</v>
+        <v>29.54471541160351</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.86981277042945</v>
+        <v>18.8691908756237</v>
       </c>
       <c r="C3" t="n">
-        <v>25.91813939211579</v>
+        <v>21.29410770511332</v>
       </c>
       <c r="D3" t="n">
-        <v>43.4619708670063</v>
+        <v>68.57998588016095</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.28517416478385</v>
+        <v>28.15456066239003</v>
       </c>
       <c r="C4" t="n">
-        <v>42.27012915405066</v>
+        <v>57.54710517983528</v>
       </c>
       <c r="D4" t="n">
-        <v>42.12973923234337</v>
+        <v>69.5185366854209</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.42913122440965</v>
+        <v>28.98610096788708</v>
       </c>
       <c r="C5" t="n">
-        <v>56.00870652728054</v>
+        <v>66.04707680320418</v>
       </c>
       <c r="D5" t="n">
-        <v>30.40963513904496</v>
+        <v>42.77965621255477</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.86043726174349</v>
+        <v>21.73589417202438</v>
       </c>
       <c r="C6" t="n">
-        <v>42.58625191481815</v>
+        <v>44.43782808502763</v>
       </c>
       <c r="D6" t="n">
-        <v>31.91956310817655</v>
+        <v>33.81139093426016</v>
       </c>
     </row>
     <row r="7">
@@ -6137,10 +6137,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.71403368062369</v>
+        <v>11.0191362324662</v>
       </c>
       <c r="C7" t="n">
-        <v>28.80545939030566</v>
+        <v>25.3919226226395</v>
       </c>
       <c r="D7" t="n">
         <v>33.59638818703009</v>
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.175193059712437</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>21.02903582496668</v>
+        <v>20.27799883121787</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>32.46148784092078</v>
       </c>
     </row>
     <row r="9">
@@ -6171,7 +6171,7 @@
         <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -6185,7 +6185,7 @@
         <v>25.0542014123786</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>35.00617789032851</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -6213,7 +6213,7 @@
         <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6238,10 +6238,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6255,7 +6255,7 @@
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6283,7 +6283,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6325,7 +6325,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.303732969508609</v>
+        <v>7.293261603726077</v>
       </c>
       <c r="C21" t="n">
-        <v>77.60216280102897</v>
+        <v>76.57924683912381</v>
       </c>
       <c r="D21" t="n">
-        <v>6.390766348320033</v>
+        <v>6.381603903260317</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.025967408666922</v>
+        <v>4.166537256823463</v>
       </c>
       <c r="C2" t="n">
-        <v>7.329728359906686</v>
+        <v>5.85416156042373</v>
       </c>
       <c r="D2" t="n">
-        <v>17.01270596689298</v>
+        <v>36.3354642818787</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.70429831903924</v>
+        <v>19.63004534641497</v>
       </c>
       <c r="C3" t="n">
-        <v>28.01907947920397</v>
+        <v>23.2232419439583</v>
       </c>
       <c r="D3" t="n">
-        <v>47.6442160870977</v>
+        <v>76.30143157406211</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.29190752999335</v>
+        <v>33.36175048571511</v>
       </c>
       <c r="C4" t="n">
-        <v>56.09215508214152</v>
+        <v>55.08390018988003</v>
       </c>
       <c r="D4" t="n">
-        <v>55.13495107050087</v>
+        <v>87.61607386550659</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.69406423583604</v>
+        <v>36.32466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>68.62416452685206</v>
+        <v>89.51084693470295</v>
       </c>
       <c r="D5" t="n">
-        <v>39.19627709205391</v>
+        <v>58.92940594741481</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.62021217383928</v>
+        <v>31.67805317293184</v>
       </c>
       <c r="C6" t="n">
-        <v>69.47435803872979</v>
+        <v>78.24921901928779</v>
       </c>
       <c r="D6" t="n">
-        <v>34.41516577237194</v>
+        <v>39.92964262712628</v>
       </c>
     </row>
     <row r="7">
@@ -6448,10 +6448,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.21226279276233</v>
+        <v>19.10382857693868</v>
       </c>
       <c r="C7" t="n">
-        <v>47.72962813736718</v>
+        <v>46.65166915810418</v>
       </c>
       <c r="D7" t="n">
         <v>35.81219275551515</v>
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.18210635137117</v>
+        <v>9.262789589568655</v>
       </c>
       <c r="C8" t="n">
-        <v>31.12631096314512</v>
+        <v>28.03871443328891</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>34.63115026730623</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>25.62656032395449</v>
+        <v>25.07187287105504</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -6490,10 +6490,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
         <v>34.73423377625215</v>
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6552,7 +6552,7 @@
         <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6608,7 +6608,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.523492718726416</v>
+        <v>7.506957154346421</v>
       </c>
       <c r="C21" t="n">
-        <v>87.46060285519458</v>
+        <v>86.33000727498383</v>
       </c>
       <c r="D21" t="n">
-        <v>7.523492718726416</v>
+        <v>7.506957154346421</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_75_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_75_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497634382119</v>
+        <v>10.84497646875505</v>
       </c>
       <c r="C21" t="n">
-        <v>37.7890719823508</v>
+        <v>37.78907241767995</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.133558745506572</v>
+        <v>7.10392638792992</v>
       </c>
       <c r="C2" t="n">
-        <v>8.408669086873932</v>
+        <v>10.01284483561322</v>
       </c>
       <c r="D2" t="n">
-        <v>41.90491900807086</v>
+        <v>26.97253642647687</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.69461971071701</v>
+        <v>21.11248437982766</v>
       </c>
       <c r="C3" t="n">
-        <v>22.90908267859932</v>
+        <v>19.13917149429157</v>
       </c>
       <c r="D3" t="n">
-        <v>86.94357668809754</v>
+        <v>81.13163027895641</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.63351467334223</v>
+        <v>43.38048580755381</v>
       </c>
       <c r="C4" t="n">
-        <v>56.19425684338318</v>
+        <v>54.4330014619644</v>
       </c>
       <c r="D4" t="n">
-        <v>105.1520513587631</v>
+        <v>111.0867162309351</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.71231653158924</v>
+        <v>54.0697548113931</v>
       </c>
       <c r="C5" t="n">
-        <v>96.13764393836894</v>
+        <v>95.10680884890976</v>
       </c>
       <c r="D5" t="n">
-        <v>75.49639845657973</v>
+        <v>85.51022503989719</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.6139207769863</v>
+        <v>49.67054334866313</v>
       </c>
       <c r="C6" t="n">
-        <v>111.6178417389326</v>
+        <v>113.429166253268</v>
       </c>
       <c r="D6" t="n">
-        <v>49.14727182229959</v>
+        <v>54.66174867705392</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.86534600026472</v>
+        <v>35.51275970571987</v>
       </c>
       <c r="C7" t="n">
-        <v>80.30794395509334</v>
+        <v>90.78810069792803</v>
       </c>
       <c r="D7" t="n">
-        <v>39.34550274309942</v>
+        <v>41.50142070162541</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.0207398749762</v>
+        <v>17.94143929511046</v>
       </c>
       <c r="C8" t="n">
-        <v>45.72980806381643</v>
+        <v>53.49052366588747</v>
       </c>
       <c r="D8" t="n">
-        <v>36.30012136452581</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.765624340592267</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>30.61874740004951</v>
+        <v>31.61718481526852</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>34.39062207976576</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>29.18245050873644</v>
+        <v>28.47068342315751</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.98864530037232</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -951,7 +951,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -965,7 +965,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.706592246426005</v>
+        <v>7.676910603989616</v>
       </c>
       <c r="C21" t="n">
-        <v>95.36907904952182</v>
+        <v>93.08254107337409</v>
       </c>
       <c r="D21" t="n">
-        <v>8.669916277229255</v>
+        <v>7.676910603989616</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.043638867343365</v>
+        <v>8.321293541195965</v>
       </c>
       <c r="C2" t="n">
-        <v>8.501935118777377</v>
+        <v>9.669233139126835</v>
       </c>
       <c r="D2" t="n">
-        <v>33.96061658530567</v>
+        <v>31.15674514197677</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.87133429748144</v>
+        <v>22.545836028028</v>
       </c>
       <c r="C3" t="n">
-        <v>27.92581344730052</v>
+        <v>29.21190293986384</v>
       </c>
       <c r="D3" t="n">
-        <v>97.76734512741861</v>
+        <v>82.98222470146165</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.43832680664636</v>
+        <v>41.33845058272045</v>
       </c>
       <c r="C4" t="n">
-        <v>56.6664774891259</v>
+        <v>51.05088062083414</v>
       </c>
       <c r="D4" t="n">
-        <v>120.6715190674967</v>
+        <v>124.0025890280061</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.15472489330606</v>
+        <v>58.90486225480863</v>
       </c>
       <c r="C5" t="n">
-        <v>98.81290643244149</v>
+        <v>96.60397409788617</v>
       </c>
       <c r="D5" t="n">
-        <v>93.87962421860125</v>
+        <v>101.7581495451819</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.75104666041137</v>
+        <v>60.37748381117885</v>
       </c>
       <c r="C6" t="n">
-        <v>131.7034180201181</v>
+        <v>131.5021597407475</v>
       </c>
       <c r="D6" t="n">
-        <v>59.4516957260741</v>
+        <v>67.05925868628265</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.96811071404115</v>
+        <v>46.8912155979404</v>
       </c>
       <c r="C7" t="n">
-        <v>118.0963948392573</v>
+        <v>124.204829055081</v>
       </c>
       <c r="D7" t="n">
-        <v>44.19631814978291</v>
+        <v>46.47200932822701</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.61455836732527</v>
+        <v>27.20422888467911</v>
       </c>
       <c r="C8" t="n">
-        <v>74.85335371029805</v>
+        <v>84.9506288484765</v>
       </c>
       <c r="D8" t="n">
-        <v>38.21943812632832</v>
+        <v>38.63668090063322</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.31562403914873</v>
+        <v>12.7578114166873</v>
       </c>
       <c r="C9" t="n">
-        <v>42.93280885441725</v>
+        <v>47.48124596819272</v>
       </c>
       <c r="D9" t="n">
-        <v>35.94374694788421</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
         <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>31.98534020436108</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>31.02617269731195</v>
+        <v>30.37527396939631</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>28.09761929554372</v>
+        <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1262,7 +1262,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.11939767148639</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -1276,7 +1276,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -1290,7 +1290,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
         <v>27.27884171020187</v>
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.890844756452964</v>
+        <v>7.856498615952118</v>
       </c>
       <c r="C21" t="n">
-        <v>104.5536930230018</v>
+        <v>101.1524196803835</v>
       </c>
       <c r="D21" t="n">
-        <v>9.863555945566205</v>
+        <v>8.838560942946133</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.082148011987242</v>
+        <v>9.314822217893736</v>
       </c>
       <c r="C2" t="n">
-        <v>9.200939484201108</v>
+        <v>13.55499055253571</v>
       </c>
       <c r="D2" t="n">
-        <v>39.2591089451257</v>
+        <v>37.47821860962198</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.1917849596934</v>
+        <v>24.55351008321273</v>
       </c>
       <c r="C3" t="n">
-        <v>30.18874190558942</v>
+        <v>33.2125248346696</v>
       </c>
       <c r="D3" t="n">
-        <v>100.5702348230433</v>
+        <v>86.40361545076178</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.23863111205676</v>
+        <v>41.15977250054753</v>
       </c>
       <c r="C4" t="n">
-        <v>62.67771868222911</v>
+        <v>60.25280185273949</v>
       </c>
       <c r="D4" t="n">
-        <v>137.5055469522167</v>
+        <v>132.2473062482708</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.2837347531899</v>
+        <v>60.42657119639119</v>
       </c>
       <c r="C5" t="n">
-        <v>100.187353218387</v>
+        <v>94.32141068551232</v>
       </c>
       <c r="D5" t="n">
-        <v>110.0048302608551</v>
+        <v>117.3679380427062</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.11080828852221</v>
+        <v>68.0252984272615</v>
       </c>
       <c r="C6" t="n">
-        <v>143.2958949118645</v>
+        <v>141.4040670857809</v>
       </c>
       <c r="D6" t="n">
-        <v>72.25172229404403</v>
+        <v>80.54356340411259</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>47.07087542781757</v>
+        <v>57.19171251089794</v>
       </c>
       <c r="C7" t="n">
-        <v>148.8781123582118</v>
+        <v>151.6328964163284</v>
       </c>
       <c r="D7" t="n">
-        <v>49.34656660626167</v>
+        <v>52.81998998388688</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>30.54217107911827</v>
+        <v>36.96770980341364</v>
       </c>
       <c r="C8" t="n">
-        <v>110.0686438616311</v>
+        <v>118.580396457451</v>
       </c>
       <c r="D8" t="n">
-        <v>40.97324043674063</v>
+        <v>41.80772598535042</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.30781111524376</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="C9" t="n">
-        <v>65.00936947981526</v>
+        <v>72.44218134866787</v>
       </c>
       <c r="D9" t="n">
-        <v>37.05312185368311</v>
+        <v>36.72030938194344</v>
       </c>
     </row>
     <row r="10">
@@ -1514,10 +1514,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>9.110618695410402</v>
       </c>
       <c r="C10" t="n">
-        <v>40.9977841293468</v>
+        <v>42.84837855185204</v>
       </c>
       <c r="D10" t="n">
         <v>36.44247478164161</v>
@@ -1531,10 +1531,10 @@
         <v>5.508586368528851</v>
       </c>
       <c r="C11" t="n">
-        <v>35.36157055926586</v>
+        <v>34.65078522139116</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.41280136633594</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>36.23336252063703</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.69925071179776</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1570,10 +1570,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>28.27040689149115</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
         <v>31.34327720578367</v>
@@ -1587,7 +1587,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -1618,7 +1618,7 @@
         <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.060122198478259</v>
+        <v>8.020621210695369</v>
       </c>
       <c r="C21" t="n">
-        <v>112.8417107786956</v>
+        <v>109.2809639957244</v>
       </c>
       <c r="D21" t="n">
-        <v>11.0826680229076</v>
+        <v>10.02577651336921</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.049349427119598</v>
+        <v>8.551022503989719</v>
       </c>
       <c r="C2" t="n">
-        <v>6.182065293642165</v>
+        <v>9.216647447469056</v>
       </c>
       <c r="D2" t="n">
-        <v>32.1787445020977</v>
+        <v>30.81116995008189</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.18749811597792</v>
+        <v>28.96646601380214</v>
       </c>
       <c r="C3" t="n">
-        <v>44.5860719883689</v>
+        <v>49.58316780298516</v>
       </c>
       <c r="D3" t="n">
-        <v>108.4242164570177</v>
+        <v>94.42449419445822</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.67484588791183</v>
+        <v>29.02242563294421</v>
       </c>
       <c r="C4" t="n">
-        <v>84.91037719260238</v>
+        <v>80.04778081346792</v>
       </c>
       <c r="D4" t="n">
-        <v>130.0648811017302</v>
+        <v>128.5078292427947</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.6122760767473</v>
+        <v>38.31270415823178</v>
       </c>
       <c r="C5" t="n">
-        <v>85.60839981032187</v>
+        <v>84.47938995043805</v>
       </c>
       <c r="D5" t="n">
-        <v>73.77833997414781</v>
+        <v>79.66882619962867</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.22270216461057</v>
+        <v>35.50196048097316</v>
       </c>
       <c r="C6" t="n">
-        <v>98.05303370935445</v>
+        <v>99.86435822368982</v>
       </c>
       <c r="D6" t="n">
-        <v>32.48308629041422</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.24167416616073</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="C7" t="n">
-        <v>77.37350006709961</v>
+        <v>83.36216106300515</v>
       </c>
       <c r="D7" t="n">
-        <v>28.80545939030566</v>
+        <v>29.34443887993716</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.26555490623215</v>
+        <v>13.01797455831271</v>
       </c>
       <c r="C8" t="n">
-        <v>47.89947049020188</v>
+        <v>53.3236265561655</v>
       </c>
       <c r="D8" t="n">
-        <v>27.28767743954009</v>
+        <v>27.03733177495716</v>
       </c>
     </row>
     <row r="9">
@@ -1811,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>6.545311944213482</v>
       </c>
       <c r="C9" t="n">
-        <v>31.28437234352885</v>
+        <v>32.61562223048752</v>
       </c>
       <c r="D9" t="n">
         <v>27.73437264497238</v>
@@ -1828,10 +1828,10 @@
         <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>27.75891633757857</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>29.04009709162065</v>
+        <v>28.32833000604172</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>26.90381408717959</v>
+        <v>26.68684784454105</v>
       </c>
     </row>
     <row r="13">
@@ -1867,10 +1867,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
         <v>25.75615102091507</v>
@@ -1884,7 +1884,7 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
         <v>23.66110142005238</v>
@@ -1915,7 +1915,7 @@
         <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
-        <v>9.628981483252716</v>
+        <v>9.027170140549421</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.673119072214817</v>
+        <v>5.308309836862503</v>
       </c>
       <c r="C2" t="n">
-        <v>3.385066084243002</v>
+        <v>4.434554380082843</v>
       </c>
       <c r="D2" t="n">
-        <v>22.33574201931918</v>
+        <v>21.48751200284994</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.4861704022472</v>
+        <v>29.96784867213389</v>
       </c>
       <c r="C3" t="n">
-        <v>34.68514639103981</v>
+        <v>43.55032816038851</v>
       </c>
       <c r="D3" t="n">
-        <v>109.3126981293611</v>
+        <v>97.09484795000955</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.12376663065989</v>
+        <v>40.35572113076939</v>
       </c>
       <c r="C4" t="n">
-        <v>100.9914045881651</v>
+        <v>103.1993551750162</v>
       </c>
       <c r="D4" t="n">
-        <v>151.9274207276024</v>
+        <v>145.0355518437898</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.19565519724816</v>
+        <v>42.68148144213009</v>
       </c>
       <c r="C5" t="n">
-        <v>119.1596276029566</v>
+        <v>115.4289863268188</v>
       </c>
       <c r="D5" t="n">
-        <v>94.95954669327274</v>
+        <v>99.67193567365744</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.05919226635785</v>
+        <v>42.02272873258048</v>
       </c>
       <c r="C6" t="n">
-        <v>119.0241464197706</v>
+        <v>119.3059080108894</v>
       </c>
       <c r="D6" t="n">
-        <v>41.49945720621693</v>
+        <v>44.55858305264999</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.10382857693868</v>
+        <v>23.05634483423634</v>
       </c>
       <c r="C7" t="n">
-        <v>102.9450825196163</v>
+        <v>107.0772586067911</v>
       </c>
       <c r="D7" t="n">
-        <v>31.50035683846316</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.429686699290613</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>64.58918146239766</v>
+        <v>71.9326542901638</v>
       </c>
       <c r="D8" t="n">
-        <v>28.45595720759379</v>
+        <v>28.28906009787184</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>36.94218436310322</v>
+        <v>37.27499683484289</v>
       </c>
       <c r="D9" t="n">
-        <v>28.73281006019139</v>
+        <v>28.6218725696115</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>29.75186417719959</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>30.03068052520567</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
         <v>28.42257778564941</v>
@@ -2181,7 +2181,7 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
         <v>24.97566159603886</v>
@@ -2212,7 +2212,7 @@
         <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
-        <v>8.025787482217675</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.667228585989336</v>
+        <v>5.065818153913542</v>
       </c>
       <c r="C2" t="n">
-        <v>6.787803627162447</v>
+        <v>7.976700097005335</v>
       </c>
       <c r="D2" t="n">
-        <v>27.04616750429538</v>
+        <v>26.72219076189393</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.63142800474672</v>
+        <v>24.19026343264141</v>
       </c>
       <c r="C3" t="n">
-        <v>23.0219836645877</v>
+        <v>29.70768553050848</v>
       </c>
       <c r="D3" t="n">
-        <v>103.1816837163398</v>
+        <v>91.97503367236243</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.40677201139022</v>
+        <v>48.17926858591222</v>
       </c>
       <c r="C4" t="n">
-        <v>93.48692513690251</v>
+        <v>105.9561027285413</v>
       </c>
       <c r="D4" t="n">
-        <v>167.4341257161808</v>
+        <v>158.1556281633441</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.33157834879072</v>
+        <v>51.02633692822798</v>
       </c>
       <c r="C5" t="n">
-        <v>153.8398652554752</v>
+        <v>152.0727193878309</v>
       </c>
       <c r="D5" t="n">
-        <v>124.2401719724339</v>
+        <v>124.1665408946154</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.89568236810514</v>
+        <v>49.67054334866313</v>
       </c>
       <c r="C6" t="n">
-        <v>152.3122658276672</v>
+        <v>150.8632062161989</v>
       </c>
       <c r="D6" t="n">
-        <v>58.48565598509524</v>
+        <v>61.06176196103888</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.38625312059227</v>
+        <v>33.59638818703009</v>
       </c>
       <c r="C7" t="n">
-        <v>136.6013573166054</v>
+        <v>138.3979556153771</v>
       </c>
       <c r="D7" t="n">
-        <v>35.93196597543326</v>
+        <v>36.53083207502382</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.60211444233956</v>
+        <v>16.10557108816892</v>
       </c>
       <c r="C8" t="n">
-        <v>97.63480918734528</v>
+        <v>103.6431051373358</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.434374453633594</v>
+        <v>6.878124415953151</v>
       </c>
       <c r="C9" t="n">
-        <v>56.24530772400399</v>
+        <v>59.3515574602409</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>2.847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>36.72718161587318</v>
+        <v>36.86953503298896</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>30.46363126277853</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
         <v>28.8565102709265</v>
@@ -2492,7 +2492,7 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.51223562190536</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
         <v>25.75615102091507</v>
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
         <v>19.35908298004286</v>
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>10.86107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>6.955682484588652</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.770492021384499</v>
+        <v>3.036545649235384</v>
       </c>
       <c r="C2" t="n">
-        <v>3.111158474758142</v>
+        <v>3.757148464152543</v>
       </c>
       <c r="D2" t="n">
-        <v>18.66596910084461</v>
+        <v>18.64142540823844</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.52834449580081</v>
+        <v>23.80247308946392</v>
       </c>
       <c r="C3" t="n">
-        <v>26.03594911662541</v>
+        <v>32.22095965338032</v>
       </c>
       <c r="D3" t="n">
-        <v>104.2910586221387</v>
+        <v>94.24287086917256</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.78438502462675</v>
+        <v>52.91423776349458</v>
       </c>
       <c r="C4" t="n">
-        <v>90.10480429577225</v>
+        <v>104.5394407913131</v>
       </c>
       <c r="D4" t="n">
-        <v>182.2771692566883</v>
+        <v>168.5444823696839</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.44233591292137</v>
+        <v>53.38253141842033</v>
       </c>
       <c r="C5" t="n">
-        <v>181.3288009743859</v>
+        <v>187.1211124294421</v>
       </c>
       <c r="D5" t="n">
-        <v>131.1860369799801</v>
+        <v>130.7687942056752</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.25415914887547</v>
+        <v>41.05668899160162</v>
       </c>
       <c r="C6" t="n">
-        <v>185.1173653650744</v>
+        <v>181.0116964659142</v>
       </c>
       <c r="D6" t="n">
-        <v>56.91584140600459</v>
+        <v>59.25043744670351</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.982991493858314</v>
+        <v>10.65981657271187</v>
       </c>
       <c r="C7" t="n">
-        <v>137.6793162958684</v>
+        <v>141.1527396734936</v>
       </c>
       <c r="D7" t="n">
-        <v>35.69241953559704</v>
+        <v>36.11162580531042</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.422773407631881</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>72.01610284502478</v>
+        <v>75.18714792974197</v>
       </c>
       <c r="D8" t="n">
-        <v>31.71045084717197</v>
+        <v>31.54355373745002</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>27.95624762613216</v>
+        <v>28.06718511671205</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>31.8390597964283</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.1930287493049</v>
+        <v>25.33890824661018</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
         <v>23.10052348092744</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
         <v>21.04572553593887</v>
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.919578803709772</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.66664774891259</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.454770171244526</v>
+        <v>4.400193210434204</v>
       </c>
       <c r="C2" t="n">
-        <v>5.637195317785186</v>
+        <v>7.994371555681777</v>
       </c>
       <c r="D2" t="n">
-        <v>22.89730170614836</v>
+        <v>16.49630667445916</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.21218067730433</v>
+        <v>17.34748193404114</v>
       </c>
       <c r="C3" t="n">
-        <v>18.96736564604837</v>
+        <v>23.28705554473434</v>
       </c>
       <c r="D3" t="n">
-        <v>95.78912350336128</v>
+        <v>88.67145264757193</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.14250195249858</v>
+        <v>49.86394764639974</v>
       </c>
       <c r="C4" t="n">
-        <v>77.68667758475436</v>
+        <v>93.5890268981442</v>
       </c>
       <c r="D4" t="n">
-        <v>192.9850914669082</v>
+        <v>175.1683341302371</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.70159942230054</v>
+        <v>64.37810570598461</v>
       </c>
       <c r="C5" t="n">
-        <v>175.6592079823606</v>
+        <v>191.146278016854</v>
       </c>
       <c r="D5" t="n">
-        <v>158.7731474693154</v>
+        <v>154.6252634188727</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.1560664939088</v>
+        <v>52.76992085097032</v>
       </c>
       <c r="C6" t="n">
-        <v>232.6143192965351</v>
+        <v>233.0973391670245</v>
       </c>
       <c r="D6" t="n">
-        <v>77.40393424593128</v>
+        <v>79.33601372788901</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.16371518689774</v>
+        <v>22.99645822427728</v>
       </c>
       <c r="C7" t="n">
-        <v>195.6495547362341</v>
+        <v>192.7151108482404</v>
       </c>
       <c r="D7" t="n">
-        <v>41.86074036137975</v>
+        <v>42.69915290080652</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.00829594999048</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C8" t="n">
-        <v>116.8279768053704</v>
+        <v>121.4176473227242</v>
       </c>
       <c r="D8" t="n">
-        <v>33.62976760897448</v>
+        <v>33.54631905411351</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>50.58749570442963</v>
+        <v>51.14218315732908</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>29.18245050873644</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>8.266315669758143</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.359139733305085</v>
+        <v>3.110176727053895</v>
       </c>
       <c r="C2" t="n">
-        <v>2.97960428238907</v>
+        <v>4.808600255400877</v>
       </c>
       <c r="D2" t="n">
-        <v>16.66418553188536</v>
+        <v>12.62036673809275</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.90645623065607</v>
+        <v>16.50317890838888</v>
       </c>
       <c r="C3" t="n">
-        <v>20.70505908256523</v>
+        <v>27.03242303643592</v>
       </c>
       <c r="D3" t="n">
-        <v>92.81933669801469</v>
+        <v>83.954154928666</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.75212621910685</v>
+        <v>44.65675782307466</v>
       </c>
       <c r="C4" t="n">
-        <v>66.11089040398021</v>
+        <v>81.00498482510856</v>
       </c>
       <c r="D4" t="n">
-        <v>196.4948395095906</v>
+        <v>178.4355904899705</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.02758071783948</v>
+        <v>70.31767931667781</v>
       </c>
       <c r="C5" t="n">
-        <v>169.1551294417254</v>
+        <v>190.5326857016997</v>
       </c>
       <c r="D5" t="n">
-        <v>181.4515194374167</v>
+        <v>170.6522946907018</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.88438442173969</v>
+        <v>61.58503348740243</v>
       </c>
       <c r="C6" t="n">
-        <v>259.4621737645726</v>
+        <v>266.8684784454105</v>
       </c>
       <c r="D6" t="n">
-        <v>93.78635818669781</v>
+        <v>95.75868932452966</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.96598298771663</v>
+        <v>20.72076704583318</v>
       </c>
       <c r="C7" t="n">
-        <v>245.8345338819225</v>
+        <v>242.061677454502</v>
       </c>
       <c r="D7" t="n">
-        <v>48.08894779712151</v>
+        <v>47.90928796724435</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>5.340707511102648</v>
       </c>
       <c r="C8" t="n">
-        <v>153.3784438344792</v>
+        <v>155.5481062608646</v>
       </c>
       <c r="D8" t="n">
-        <v>34.71459882216722</v>
+        <v>34.63115026730623</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>59.68436993198057</v>
+        <v>58.79687000734145</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
         <v>19.96089432274615</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>7.525096153051802</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.295146206079795</v>
+        <v>3.848451000647497</v>
       </c>
       <c r="C2" t="n">
-        <v>8.566730467257669</v>
+        <v>11.22235800724529</v>
       </c>
       <c r="D2" t="n">
-        <v>27.1787034443687</v>
+        <v>12.87758463660541</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.07411410390402</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C3" t="n">
-        <v>16.49336143134641</v>
+        <v>23.25269437508571</v>
       </c>
       <c r="D3" t="n">
-        <v>85.73602701187394</v>
+        <v>76.07562960208534</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.31520743298801</v>
+        <v>38.27539774547039</v>
       </c>
       <c r="C4" t="n">
-        <v>59.53808952404782</v>
+        <v>74.11311594129596</v>
       </c>
       <c r="D4" t="n">
-        <v>196.9670601553333</v>
+        <v>178.7418957736955</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.65942532874693</v>
+        <v>69.60591223109887</v>
       </c>
       <c r="C5" t="n">
-        <v>148.6856898081795</v>
+        <v>172.542159021377</v>
       </c>
       <c r="D5" t="n">
-        <v>202.3136581526615</v>
+        <v>188.6428213710246</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>62.22905998138833</v>
+        <v>72.93600044390405</v>
       </c>
       <c r="C6" t="n">
-        <v>264.1716175018445</v>
+        <v>284.7402136535194</v>
       </c>
       <c r="D6" t="n">
-        <v>118.0178550229176</v>
+        <v>117.494583496554</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.39865598784899</v>
+        <v>38.0279973240002</v>
       </c>
       <c r="C7" t="n">
-        <v>297.9358845463008</v>
+        <v>298.1155443761779</v>
       </c>
       <c r="D7" t="n">
-        <v>57.85046522044755</v>
+        <v>58.50921792999716</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.262789589568655</v>
+        <v>10.51451791248334</v>
       </c>
       <c r="C8" t="n">
-        <v>221.5559131558989</v>
+        <v>217.8007281871549</v>
       </c>
       <c r="D8" t="n">
-        <v>38.46978379091126</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.662499773917349</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>106.8328034284336</v>
+        <v>107.1656159001733</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>44.55661955724149</v>
+        <v>43.98720588877834</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.8983245115816</v>
+        <v>27.36523550817559</v>
       </c>
       <c r="D11" t="n">
-        <v>24.6997904911455</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3767,7 +3767,7 @@
         <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.245477983790708</v>
+        <v>7.299294181075035</v>
       </c>
       <c r="C2" t="n">
-        <v>2.951133598965912</v>
+        <v>2.447497026687298</v>
       </c>
       <c r="D2" t="n">
-        <v>5.219952543480291</v>
+        <v>16.12913303307085</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.070906818884023</v>
+        <v>2.787181732356694</v>
       </c>
       <c r="C2" t="n">
-        <v>4.934263961544469</v>
+        <v>6.463826884761</v>
       </c>
       <c r="D2" t="n">
-        <v>20.00310947402876</v>
+        <v>9.580875845744622</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.34471661737765</v>
+        <v>17.90707812546182</v>
       </c>
       <c r="C3" t="n">
-        <v>23.84174299763379</v>
+        <v>32.65783738177014</v>
       </c>
       <c r="D3" t="n">
-        <v>96.0934652916778</v>
+        <v>81.25434874198726</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.4015034199705</v>
+        <v>52.99081408442584</v>
       </c>
       <c r="C4" t="n">
-        <v>85.76547944300135</v>
+        <v>105.3690176014017</v>
       </c>
       <c r="D4" t="n">
-        <v>201.0894187654657</v>
+        <v>183.119508786932</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.66827675361837</v>
+        <v>42.36241343824987</v>
       </c>
       <c r="C5" t="n">
-        <v>221.8995248523854</v>
+        <v>248.799411948748</v>
       </c>
       <c r="D5" t="n">
-        <v>180.911558200081</v>
+        <v>170.9222753093697</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.0855762811855</v>
+        <v>23.58747034223387</v>
       </c>
       <c r="C6" t="n">
-        <v>247.9904518404486</v>
+        <v>249.3590081401686</v>
       </c>
       <c r="D6" t="n">
-        <v>90.96874227550947</v>
+        <v>91.08949724313183</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.108434215823654</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>155.7650725035032</v>
+        <v>153.1300616653047</v>
       </c>
       <c r="D7" t="n">
-        <v>34.37491411649782</v>
+        <v>33.95570784678443</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.835868206941535</v>
+        <v>1.919316761802514</v>
       </c>
       <c r="C8" t="n">
-        <v>78.69198723390308</v>
+        <v>78.94233289848603</v>
       </c>
       <c r="D8" t="n">
-        <v>24.61732368398877</v>
+        <v>24.53387512912779</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>33.50312215512664</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>20.1906232855399</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.78007281871549</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>19.3600647277471</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.52575910558656</v>
+        <v>15.99267010218054</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4375,7 +4375,7 @@
         <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>5.838453597155781</v>
+        <v>5.223879534297279</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.501133297522379</v>
+        <v>7.976700097005335</v>
       </c>
       <c r="C2" t="n">
-        <v>3.376230354904781</v>
+        <v>7.671376560984576</v>
       </c>
       <c r="D2" t="n">
-        <v>19.80086944695392</v>
+        <v>24.39053996430776</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.14774518172253</v>
+        <v>15.50179625005713</v>
       </c>
       <c r="C3" t="n">
-        <v>7.554548584179206</v>
+        <v>6.165375582669969</v>
       </c>
       <c r="D3" t="n">
-        <v>7.731263170943632</v>
+        <v>16.68480223367454</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>23.93500902953724</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39970210993115</v>
+        <v>13.39755998938874</v>
       </c>
       <c r="C21" t="n">
-        <v>70.15138163434543</v>
+        <v>70.14016700327043</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576435542344841</v>
+        <v>1.57618352816338</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.444371857125311</v>
+        <v>6.21446296788231</v>
       </c>
       <c r="C2" t="n">
-        <v>6.481498343437441</v>
+        <v>5.486006171331176</v>
       </c>
       <c r="D2" t="n">
-        <v>24.0685267173148</v>
+        <v>30.163216465279</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.91198686398306</v>
+        <v>22.74218556887736</v>
       </c>
       <c r="C3" t="n">
-        <v>11.1281102276376</v>
+        <v>21.02412708644545</v>
       </c>
       <c r="D3" t="n">
-        <v>22.49183990429443</v>
+        <v>33.13889375685108</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.01797455831271</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="C4" t="n">
-        <v>12.23944862884498</v>
+        <v>9.967684441217866</v>
       </c>
       <c r="D4" t="n">
-        <v>19.11855479250239</v>
+        <v>23.81523580961913</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.473243451175969</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.4455230581666</v>
+        <v>15.43882727734837</v>
       </c>
       <c r="C21" t="n">
-        <v>86.16976021924525</v>
+        <v>86.13240481046988</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251689064877179</v>
+        <v>3.250279426810184</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.896957548783091</v>
+        <v>5.139449231732052</v>
       </c>
       <c r="C2" t="n">
-        <v>8.095491569219199</v>
+        <v>7.200137662946108</v>
       </c>
       <c r="D2" t="n">
-        <v>35.57657330649591</v>
+        <v>29.09409321535422</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.67007601811084</v>
+        <v>22.05987091442583</v>
       </c>
       <c r="C3" t="n">
-        <v>19.67422399310608</v>
+        <v>21.22047662729481</v>
       </c>
       <c r="D3" t="n">
-        <v>36.52592333650258</v>
+        <v>49.57825906446393</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.20637230653686</v>
+        <v>32.78742807873073</v>
       </c>
       <c r="C4" t="n">
-        <v>21.31374265919825</v>
+        <v>35.07195498651306</v>
       </c>
       <c r="D4" t="n">
-        <v>26.08699999724625</v>
+        <v>35.05919226635785</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.75642875835556</v>
+        <v>15.33980787885642</v>
       </c>
       <c r="C5" t="n">
-        <v>15.36435157146258</v>
+        <v>12.83635123302705</v>
       </c>
       <c r="D5" t="n">
-        <v>29.32971266437347</v>
+        <v>31.19503330244241</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.876741757621407</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.13430381349934</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.6242369756475</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5288,10 +5288,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5336,7 +5336,7 @@
         <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>31.56809743005619</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74414977476293</v>
+        <v>16.72934434976387</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1393136260539</v>
+        <v>102.0490005335596</v>
       </c>
       <c r="D21" t="n">
-        <v>5.023244932428881</v>
+        <v>4.182336087440967</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.531166565726529</v>
+        <v>7.133378819057324</v>
       </c>
       <c r="C2" t="n">
-        <v>7.170685231818704</v>
+        <v>6.450082416901544</v>
       </c>
       <c r="D2" t="n">
-        <v>26.66328589963912</v>
+        <v>21.96464138711389</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.72898088036565</v>
+        <v>19.6055016538088</v>
       </c>
       <c r="C3" t="n">
-        <v>26.57591035396116</v>
+        <v>25.08856258202724</v>
       </c>
       <c r="D3" t="n">
-        <v>55.43929285881739</v>
+        <v>60.66219064541041</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.94584931201296</v>
+        <v>37.8414652601933</v>
       </c>
       <c r="C4" t="n">
-        <v>37.19056653227767</v>
+        <v>45.14174118897259</v>
       </c>
       <c r="D4" t="n">
-        <v>37.59897357724434</v>
+        <v>51.10193150145498</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.05911015089984</v>
+        <v>32.25041208450773</v>
       </c>
       <c r="C5" t="n">
-        <v>28.56885819358219</v>
+        <v>40.86524818927349</v>
       </c>
       <c r="D5" t="n">
-        <v>32.22586839190156</v>
+        <v>36.20194659410114</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.90819874188631</v>
+        <v>13.16229147083699</v>
       </c>
       <c r="C6" t="n">
-        <v>18.55601335796896</v>
+        <v>16.38242394076653</v>
       </c>
       <c r="D6" t="n">
-        <v>38.07806645691679</v>
+        <v>38.56108632740622</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.13997331554657</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.79389940203295</v>
+        <v>31.62700229231099</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>8.707120388964958</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5599,10 +5599,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
         <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.74489413227862</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>32.63820242768521</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5686,10 +5686,10 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>37.91411459030757</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07561705803875</v>
+        <v>18.05121714972874</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9218827119671</v>
+        <v>117.7627023577542</v>
       </c>
       <c r="D21" t="n">
-        <v>6.885949355443333</v>
+        <v>6.017072383242914</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.751078051477815</v>
+        <v>7.859872120199964</v>
       </c>
       <c r="C2" t="n">
-        <v>4.848851911274997</v>
+        <v>5.506622873120359</v>
       </c>
       <c r="D2" t="n">
-        <v>27.20128364156637</v>
+        <v>32.30440820824129</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.10557108816893</v>
+        <v>19.87548227247668</v>
       </c>
       <c r="C3" t="n">
-        <v>25.70706363570273</v>
+        <v>23.54721868635975</v>
       </c>
       <c r="D3" t="n">
-        <v>59.6215380789088</v>
+        <v>60.08786823842603</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.62830283518473</v>
+        <v>27.40156017323272</v>
       </c>
       <c r="C4" t="n">
-        <v>45.18002934943821</v>
+        <v>46.04789431999239</v>
       </c>
       <c r="D4" t="n">
-        <v>48.49833658979244</v>
+        <v>60.20175097211866</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.03394456348791</v>
+        <v>27.51347941151687</v>
       </c>
       <c r="C5" t="n">
-        <v>37.35550014659114</v>
+        <v>47.02571503342222</v>
       </c>
       <c r="D5" t="n">
-        <v>31.24412068765475</v>
+        <v>36.81553890925539</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.3572583533546</v>
+        <v>15.41638419978766</v>
       </c>
       <c r="C6" t="n">
-        <v>22.29941735426205</v>
+        <v>28.17615911188346</v>
       </c>
       <c r="D6" t="n">
-        <v>30.59125846433062</v>
+        <v>32.04031807579891</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.509568116233099</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>15.63040519931347</v>
+        <v>14.55244622005047</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>30.84160412891355</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -5854,10 +5854,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.18749811597791</v>
+        <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
         <v>29.95312245657017</v>
@@ -5871,10 +5871,10 @@
         <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
         <v>34.29539255245382</v>
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.52696183746906</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6000,7 +6000,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.067357470264312</v>
+        <v>7.054004588592273</v>
       </c>
       <c r="C21" t="n">
-        <v>66.25647628372792</v>
+        <v>66.13129301805256</v>
       </c>
       <c r="D21" t="n">
-        <v>5.300518102698234</v>
+        <v>4.40875286787017</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.798201941281662</v>
+        <v>6.510950774564847</v>
       </c>
       <c r="C2" t="n">
-        <v>6.270422587024377</v>
+        <v>5.585162689460105</v>
       </c>
       <c r="D2" t="n">
-        <v>29.54471541160351</v>
+        <v>28.4245412810579</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.8691908756237</v>
+        <v>24.47497026687298</v>
       </c>
       <c r="C3" t="n">
-        <v>21.29410770511332</v>
+        <v>22.23658550119026</v>
       </c>
       <c r="D3" t="n">
-        <v>68.57998588016095</v>
+        <v>72.70332623799754</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.15456066239003</v>
+        <v>34.33171721751096</v>
       </c>
       <c r="C4" t="n">
-        <v>57.54710517983528</v>
+        <v>54.2670860999467</v>
       </c>
       <c r="D4" t="n">
-        <v>69.5185366854209</v>
+        <v>77.15064333823558</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.98610096788708</v>
+        <v>35.85833489761475</v>
       </c>
       <c r="C5" t="n">
-        <v>66.04707680320418</v>
+        <v>70.34222300928397</v>
       </c>
       <c r="D5" t="n">
-        <v>42.77965621255477</v>
+        <v>51.5908418581699</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.73589417202438</v>
+        <v>27.81389420901639</v>
       </c>
       <c r="C6" t="n">
-        <v>44.43782808502763</v>
+        <v>55.54728510628455</v>
       </c>
       <c r="D6" t="n">
-        <v>33.81139093426016</v>
+        <v>36.99127174831558</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.0191362324662</v>
+        <v>13.1750541909922</v>
       </c>
       <c r="C7" t="n">
-        <v>25.3919226226395</v>
+        <v>29.8235317596096</v>
       </c>
       <c r="D7" t="n">
-        <v>33.59638818703009</v>
+        <v>33.35684174719388</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>20.27799883121787</v>
+        <v>19.19316761802514</v>
       </c>
       <c r="D8" t="n">
-        <v>32.46148784092078</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>25.0542014123786</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>19.66637001147211</v>
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6266,7 +6266,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.293261603726077</v>
+        <v>7.274586704205594</v>
       </c>
       <c r="C21" t="n">
-        <v>76.57924683912381</v>
+        <v>75.47383705613304</v>
       </c>
       <c r="D21" t="n">
-        <v>6.381603903260317</v>
+        <v>5.455940028154195</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.166537256823463</v>
+        <v>5.639158813193679</v>
       </c>
       <c r="C2" t="n">
-        <v>5.85416156042373</v>
+        <v>4.378594760940774</v>
       </c>
       <c r="D2" t="n">
-        <v>36.3354642818787</v>
+        <v>26.778150381036</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.63004534641497</v>
+        <v>23.39504779220149</v>
       </c>
       <c r="C3" t="n">
-        <v>23.2232419439583</v>
+        <v>21.93224371287374</v>
       </c>
       <c r="D3" t="n">
-        <v>76.30143157406211</v>
+        <v>78.57417750939346</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.36175048571511</v>
+        <v>42.06592563156733</v>
       </c>
       <c r="C4" t="n">
-        <v>55.08390018988003</v>
+        <v>55.14771379065608</v>
       </c>
       <c r="D4" t="n">
-        <v>87.61607386550659</v>
+        <v>96.28196085089319</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.32466505713199</v>
+        <v>44.32590884674349</v>
       </c>
       <c r="C5" t="n">
-        <v>89.51084693470295</v>
+        <v>87.47372044839082</v>
       </c>
       <c r="D5" t="n">
-        <v>58.92940594741481</v>
+        <v>67.17608666308801</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.67805317293184</v>
+        <v>39.36611944488861</v>
       </c>
       <c r="C6" t="n">
-        <v>78.24921901928779</v>
+        <v>86.46055681760812</v>
       </c>
       <c r="D6" t="n">
-        <v>39.92964262712628</v>
+        <v>45.12210623488766</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.10382857693868</v>
+        <v>23.71509754378595</v>
       </c>
       <c r="C7" t="n">
-        <v>46.65166915810418</v>
+        <v>56.95216607106171</v>
       </c>
       <c r="D7" t="n">
-        <v>35.81219275551515</v>
+        <v>36.83026512481909</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.262789589568655</v>
+        <v>10.59796646734432</v>
       </c>
       <c r="C8" t="n">
-        <v>28.03871443328891</v>
+        <v>30.54217107911827</v>
       </c>
       <c r="D8" t="n">
-        <v>34.63115026730623</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>25.07187287105504</v>
+        <v>24.29531043699581</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6546,10 +6546,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6577,7 +6577,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
         <v>27.27884171020187</v>
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.506957154346421</v>
+        <v>7.482591759918953</v>
       </c>
       <c r="C21" t="n">
-        <v>86.33000727498383</v>
+        <v>84.17915729908822</v>
       </c>
       <c r="D21" t="n">
-        <v>7.506957154346421</v>
+        <v>6.547267789929084</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_75_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_75_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497646875505</v>
+        <v>10.84497641281274</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907241767995</v>
+        <v>37.78907222275029</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.10392638792992</v>
+        <v>0.9169523557665208</v>
       </c>
       <c r="C2" t="n">
-        <v>10.01284483561322</v>
+        <v>4.664283342876596</v>
       </c>
       <c r="D2" t="n">
-        <v>26.97253642647687</v>
+        <v>12.61840324268425</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.11248437982766</v>
+        <v>6.877142668248907</v>
       </c>
       <c r="C3" t="n">
-        <v>19.13917149429157</v>
+        <v>50.45201452124359</v>
       </c>
       <c r="D3" t="n">
-        <v>81.13163027895641</v>
+        <v>69.18376071827272</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.38048580755381</v>
+        <v>11.19290557611789</v>
       </c>
       <c r="C4" t="n">
-        <v>54.4330014619644</v>
+        <v>137.6969877545449</v>
       </c>
       <c r="D4" t="n">
-        <v>111.0867162309351</v>
+        <v>84.71893639027425</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.0697548113931</v>
+        <v>10.92194320974577</v>
       </c>
       <c r="C5" t="n">
-        <v>95.10680884890976</v>
+        <v>152.9562923216531</v>
       </c>
       <c r="D5" t="n">
-        <v>85.51022503989719</v>
+        <v>49.75006491270713</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.67054334866313</v>
+        <v>8.291841110068562</v>
       </c>
       <c r="C6" t="n">
-        <v>113.429166253268</v>
+        <v>106.7071397222901</v>
       </c>
       <c r="D6" t="n">
-        <v>54.66174867705392</v>
+        <v>29.98748362621883</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.51275970571987</v>
+        <v>5.689227946110266</v>
       </c>
       <c r="C7" t="n">
-        <v>90.78810069792803</v>
+        <v>54.07760879302705</v>
       </c>
       <c r="D7" t="n">
-        <v>41.50142070162541</v>
+        <v>29.8235317596096</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.94143929511046</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>53.49052366588747</v>
+        <v>30.37527396939631</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>29.95803119509142</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>31.61718481526852</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>28.47068342315751</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>37.29659528433633</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>37.84931924182727</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>37.5351599764683</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>27.04125876577415</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>22.31905230834699</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>84.25358797846125</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.676910603989616</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>93.08254107337409</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.676910603989616</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.321293541195965</v>
+        <v>0.9856746950637977</v>
       </c>
       <c r="C2" t="n">
-        <v>9.669233139126835</v>
+        <v>4.269620765769378</v>
       </c>
       <c r="D2" t="n">
-        <v>31.15674514197677</v>
+        <v>16.20767284941059</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.545836028028</v>
+        <v>4.967643383488861</v>
       </c>
       <c r="C3" t="n">
-        <v>29.21190293986384</v>
+        <v>32.05406254365836</v>
       </c>
       <c r="D3" t="n">
-        <v>82.98222470146165</v>
+        <v>64.0492202250619</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.33845058272045</v>
+        <v>12.32878766993144</v>
       </c>
       <c r="C4" t="n">
-        <v>51.05088062083414</v>
+        <v>132.7067641738583</v>
       </c>
       <c r="D4" t="n">
-        <v>124.0025890280061</v>
+        <v>98.57925047883073</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.90486225480863</v>
+        <v>13.76901155206152</v>
       </c>
       <c r="C5" t="n">
-        <v>96.60397409788617</v>
+        <v>205.6025129618883</v>
       </c>
       <c r="D5" t="n">
-        <v>101.7581495451819</v>
+        <v>66.6852128109646</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.37748381117885</v>
+        <v>11.23021198887927</v>
       </c>
       <c r="C6" t="n">
-        <v>131.5021597407475</v>
+        <v>175.8192328581528</v>
       </c>
       <c r="D6" t="n">
-        <v>67.05925868628265</v>
+        <v>37.47429161880501</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>46.8912155979404</v>
+        <v>7.60559946480004</v>
       </c>
       <c r="C7" t="n">
-        <v>124.204829055081</v>
+        <v>102.7654226897391</v>
       </c>
       <c r="D7" t="n">
-        <v>46.47200932822701</v>
+        <v>31.68001666834032</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.20422888467911</v>
+        <v>6.342090169434394</v>
       </c>
       <c r="C8" t="n">
-        <v>84.9506288484765</v>
+        <v>49.98568436172635</v>
       </c>
       <c r="D8" t="n">
-        <v>38.63668090063322</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.7578114166873</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>47.48124596819272</v>
+        <v>35.16718451382499</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>35.83280945730432</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.8329640215578</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>38.15071578703105</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>38.20471191076462</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.37527396939631</v>
+        <v>28.20561154301086</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>38.40302494702248</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>50.82998738737861</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>45.13585070274711</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.856498615952118</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>101.1524196803835</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.838560942946133</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.314822217893736</v>
+        <v>0.5360342465187585</v>
       </c>
       <c r="C2" t="n">
-        <v>13.55499055253571</v>
+        <v>1.86532063806894</v>
       </c>
       <c r="D2" t="n">
-        <v>37.47821860962198</v>
+        <v>11.05742439293182</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.55351008321273</v>
+        <v>4.771293842639499</v>
       </c>
       <c r="C3" t="n">
-        <v>33.2125248346696</v>
+        <v>26.93424826601124</v>
       </c>
       <c r="D3" t="n">
-        <v>86.40361545076178</v>
+        <v>64.44682804528188</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.15977250054753</v>
+        <v>13.55400880483146</v>
       </c>
       <c r="C4" t="n">
-        <v>60.25280185273949</v>
+        <v>125.9425224915978</v>
       </c>
       <c r="D4" t="n">
-        <v>132.2473062482708</v>
+        <v>108.4320704386517</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.42657119639119</v>
+        <v>13.84264262988003</v>
       </c>
       <c r="C5" t="n">
-        <v>94.32141068551232</v>
+        <v>244.0133918905448</v>
       </c>
       <c r="D5" t="n">
-        <v>117.3679380427062</v>
+        <v>73.53290304808611</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>68.0252984272615</v>
+        <v>9.45913913041802</v>
       </c>
       <c r="C6" t="n">
-        <v>141.4040670857809</v>
+        <v>216.5539086027615</v>
       </c>
       <c r="D6" t="n">
-        <v>80.54356340411259</v>
+        <v>38.03781480104267</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>57.19171251089794</v>
+        <v>4.19206269713388</v>
       </c>
       <c r="C7" t="n">
-        <v>151.6328964163284</v>
+        <v>93.6626579759627</v>
       </c>
       <c r="D7" t="n">
-        <v>52.81998998388688</v>
+        <v>32.99752208743954</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>36.96770980341364</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>118.580396457451</v>
+        <v>42.55876297909923</v>
       </c>
       <c r="D8" t="n">
-        <v>41.80772598535042</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18.74843590800133</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>72.44218134866787</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>36.72030938194344</v>
+        <v>39.93749660876023</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.110618695410402</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>42.84837855185204</v>
+        <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>34.65078522139116</v>
+        <v>22.56743447752142</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>30.74146586308036</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>18.27523351455437</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>43.91652005407257</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>39.05883241345935</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.020621210695369</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109.2809639957244</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10.02577651336921</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.551022503989719</v>
+        <v>0.4034983064454391</v>
       </c>
       <c r="C2" t="n">
-        <v>9.216647447469056</v>
+        <v>5.324999547834699</v>
       </c>
       <c r="D2" t="n">
-        <v>30.81116995008189</v>
+        <v>10.0943298950657</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.96646601380214</v>
+        <v>3.318307240354219</v>
       </c>
       <c r="C3" t="n">
-        <v>49.58316780298516</v>
+        <v>16.36573422979433</v>
       </c>
       <c r="D3" t="n">
-        <v>94.42449419445822</v>
+        <v>59.31228755207106</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.02242563294421</v>
+        <v>11.48644813968768</v>
       </c>
       <c r="C4" t="n">
-        <v>80.04778081346792</v>
+        <v>96.6137915749286</v>
       </c>
       <c r="D4" t="n">
-        <v>128.5078292427947</v>
+        <v>114.7751423557904</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.31270415823178</v>
+        <v>16.86151682043897</v>
       </c>
       <c r="C5" t="n">
-        <v>84.47938995043805</v>
+        <v>240.4054690774377</v>
       </c>
       <c r="D5" t="n">
-        <v>79.66882619962867</v>
+        <v>92.01430358053231</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.50196048097316</v>
+        <v>13.32329809433347</v>
       </c>
       <c r="C6" t="n">
-        <v>99.86435822368982</v>
+        <v>297.6609951891118</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>49.3887817575443</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.49362347325367</v>
+        <v>6.707300315414209</v>
       </c>
       <c r="C7" t="n">
-        <v>83.36216106300515</v>
+        <v>191.7569250888955</v>
       </c>
       <c r="D7" t="n">
-        <v>29.34443887993716</v>
+        <v>36.17151241526948</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.01797455831271</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>53.3236265561655</v>
+        <v>77.35681035612741</v>
       </c>
       <c r="D8" t="n">
-        <v>27.03733177495716</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.545311944213482</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>32.61562223048752</v>
+        <v>36.72030938194344</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>40.60312155223957</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>29.04009709162065</v>
       </c>
       <c r="D10" t="n">
-        <v>28.32833000604172</v>
+        <v>31.74481201682062</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>25.9436648324262</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>31.8076438698924</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>37.61173629739955</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.81278928812512</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>46.27762328278614</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.308309836862503</v>
+        <v>0.2915790681613027</v>
       </c>
       <c r="C2" t="n">
-        <v>4.434554380082843</v>
+        <v>2.855904071653971</v>
       </c>
       <c r="D2" t="n">
-        <v>21.48751200284994</v>
+        <v>7.796058519423921</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.96784867213389</v>
+        <v>2.518182861393069</v>
       </c>
       <c r="C3" t="n">
-        <v>43.55032816038851</v>
+        <v>18.86428213710246</v>
       </c>
       <c r="D3" t="n">
-        <v>97.09484795000955</v>
+        <v>54.85515297479053</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.35572113076939</v>
+        <v>9.686904597803279</v>
       </c>
       <c r="C4" t="n">
-        <v>103.1993551750162</v>
+        <v>74.0237769002095</v>
       </c>
       <c r="D4" t="n">
-        <v>145.0355518437898</v>
+        <v>119.1655180891821</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.68148144213009</v>
+        <v>17.94143929511046</v>
       </c>
       <c r="C5" t="n">
-        <v>115.4289863268188</v>
+        <v>223.6421270274234</v>
       </c>
       <c r="D5" t="n">
-        <v>99.67193567365744</v>
+        <v>104.9242858913779</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.02272873258048</v>
+        <v>16.14091400552181</v>
       </c>
       <c r="C6" t="n">
-        <v>119.3059080108894</v>
+        <v>341.6158034036499</v>
       </c>
       <c r="D6" t="n">
-        <v>44.55858305264999</v>
+        <v>59.97496725243766</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.05634483423634</v>
+        <v>6.886960145291375</v>
       </c>
       <c r="C7" t="n">
-        <v>107.0772586067911</v>
+        <v>271.226456504562</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>71.9326542901638</v>
+        <v>119.1645363414778</v>
       </c>
       <c r="D8" t="n">
-        <v>28.28906009787184</v>
+        <v>38.97047512007713</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>37.27499683484289</v>
+        <v>45.37343364717482</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>33.02599277086271</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>32.69612554223576</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.75013736150257</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>39.67831521483909</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.065818153913542</v>
+        <v>0.6155558105627501</v>
       </c>
       <c r="C2" t="n">
-        <v>7.976700097005335</v>
+        <v>7.022441328477434</v>
       </c>
       <c r="D2" t="n">
-        <v>26.72219076189393</v>
+        <v>11.29402558965531</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.19026343264141</v>
+        <v>1.781872083207961</v>
       </c>
       <c r="C3" t="n">
-        <v>29.70768553050848</v>
+        <v>14.96674375124262</v>
       </c>
       <c r="D3" t="n">
-        <v>91.97503367236243</v>
+        <v>49.21992115241384</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.17926858591222</v>
+        <v>7.389614969865742</v>
       </c>
       <c r="C4" t="n">
-        <v>105.9561027285413</v>
+        <v>61.21000586438014</v>
       </c>
       <c r="D4" t="n">
-        <v>158.1556281633441</v>
+        <v>119.1399926488717</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.02633692822798</v>
+        <v>16.81242943522663</v>
       </c>
       <c r="C5" t="n">
-        <v>152.0727193878309</v>
+        <v>183.8568013128214</v>
       </c>
       <c r="D5" t="n">
-        <v>124.1665408946154</v>
+        <v>119.6014140698677</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.67054334866313</v>
+        <v>19.40129813132547</v>
       </c>
       <c r="C6" t="n">
-        <v>150.8632062161989</v>
+        <v>352.2422405544174</v>
       </c>
       <c r="D6" t="n">
-        <v>61.06176196103888</v>
+        <v>74.22405343187586</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.59638818703009</v>
+        <v>11.25868267230242</v>
       </c>
       <c r="C7" t="n">
-        <v>138.3979556153771</v>
+        <v>363.9908153311389</v>
       </c>
       <c r="D7" t="n">
-        <v>36.53083207502382</v>
+        <v>45.45393695892307</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.10557108816892</v>
+        <v>5.257258956241669</v>
       </c>
       <c r="C8" t="n">
-        <v>103.6431051373358</v>
+        <v>216.6324484191012</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.878124415953151</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>59.3515574602409</v>
+        <v>84.53436782187582</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>41.04687151455913</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>36.86953503298896</v>
+        <v>40.14366362665208</v>
       </c>
       <c r="D10" t="n">
-        <v>30.46363126277853</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>17.51536079146734</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>32.96708790860789</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>38.85168364786328</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.036545649235384</v>
+        <v>0.4280419990516093</v>
       </c>
       <c r="C2" t="n">
-        <v>3.757148464152543</v>
+        <v>3.875939936366407</v>
       </c>
       <c r="D2" t="n">
-        <v>18.64142540823844</v>
+        <v>8.311476064153496</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.80247308946392</v>
+        <v>2.709623663721197</v>
       </c>
       <c r="C3" t="n">
-        <v>32.22095965338032</v>
+        <v>21.2057504117311</v>
       </c>
       <c r="D3" t="n">
-        <v>94.24287086917256</v>
+        <v>53.50034114292993</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>52.91423776349458</v>
+        <v>11.70341438232623</v>
       </c>
       <c r="C4" t="n">
-        <v>104.5394407913131</v>
+        <v>91.15134734849936</v>
       </c>
       <c r="D4" t="n">
-        <v>168.5444823696839</v>
+        <v>121.8329266016207</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.38253141842033</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="C5" t="n">
-        <v>187.1211124294421</v>
+        <v>287.725708422134</v>
       </c>
       <c r="D5" t="n">
-        <v>130.7687942056752</v>
+        <v>109.415781638307</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.05668899160162</v>
+        <v>6.963536466222627</v>
       </c>
       <c r="C6" t="n">
-        <v>181.0116964659142</v>
+        <v>315.6937370207172</v>
       </c>
       <c r="D6" t="n">
-        <v>59.25043744670351</v>
+        <v>62.10830501376597</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.65981657271187</v>
+        <v>3.473423377625215</v>
       </c>
       <c r="C7" t="n">
-        <v>141.1527396734936</v>
+        <v>152.351535735837</v>
       </c>
       <c r="D7" t="n">
-        <v>36.11162580531042</v>
+        <v>34.61446055633404</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>2.002765316663493</v>
       </c>
       <c r="C8" t="n">
-        <v>75.18714792974197</v>
+        <v>62.25262192629025</v>
       </c>
       <c r="D8" t="n">
-        <v>31.54355373745002</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.109374905798895</v>
       </c>
       <c r="C9" t="n">
-        <v>28.06718511671205</v>
+        <v>30.61874740004951</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>26.5140602485936</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>25.33890824661018</v>
+        <v>24.05772749256809</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>25.76596849795754</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.07968579496001</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.30897278939726</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>32.96708790860789</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.400193210434204</v>
+        <v>0.2248202242725195</v>
       </c>
       <c r="C2" t="n">
-        <v>7.994371555681777</v>
+        <v>2.888301745894116</v>
       </c>
       <c r="D2" t="n">
-        <v>16.49630667445916</v>
+        <v>6.428483967408114</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.34748193404114</v>
+        <v>2.086213871524472</v>
       </c>
       <c r="C3" t="n">
-        <v>23.28705554473434</v>
+        <v>18.01507037292897</v>
       </c>
       <c r="D3" t="n">
-        <v>88.67145264757193</v>
+        <v>48.11545498513618</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.86394764639974</v>
+        <v>8.014988257470959</v>
       </c>
       <c r="C4" t="n">
-        <v>93.5890268981442</v>
+        <v>69.03355331952297</v>
       </c>
       <c r="D4" t="n">
-        <v>175.1683341302371</v>
+        <v>115.9620753302247</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>64.37810570598461</v>
+        <v>11.31464229144449</v>
       </c>
       <c r="C5" t="n">
-        <v>191.146278016854</v>
+        <v>210.2658145570607</v>
       </c>
       <c r="D5" t="n">
-        <v>154.6252634188727</v>
+        <v>112.6310053697153</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.76992085097032</v>
+        <v>6.681774875103793</v>
       </c>
       <c r="C6" t="n">
-        <v>233.0973391670245</v>
+        <v>310.6622800364522</v>
       </c>
       <c r="D6" t="n">
-        <v>79.33601372788901</v>
+        <v>66.05296728942966</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.99645822427728</v>
+        <v>2.694897448157494</v>
       </c>
       <c r="C7" t="n">
-        <v>192.7151108482404</v>
+        <v>202.5365148815255</v>
       </c>
       <c r="D7" t="n">
-        <v>42.69915290080652</v>
+        <v>33.47661496711198</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.592435834017332</v>
+        <v>1.001382658331746</v>
       </c>
       <c r="C8" t="n">
-        <v>121.4176473227242</v>
+        <v>73.35127972280043</v>
       </c>
       <c r="D8" t="n">
-        <v>33.54631905411351</v>
+        <v>26.20284622634736</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>51.14218315732908</v>
+        <v>28.95468504135117</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>20.96718571959912</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>29.18245050873644</v>
+        <v>16.79770321966293</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>19.64477156197868</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>12.79413608174443</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>17.23654444346124</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>15.67163860289184</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.110176727053895</v>
+        <v>0.2238384765682727</v>
       </c>
       <c r="C2" t="n">
-        <v>4.808600255400877</v>
+        <v>11.50902833688536</v>
       </c>
       <c r="D2" t="n">
-        <v>12.62036673809275</v>
+        <v>9.342311153612648</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.50317890838888</v>
+        <v>1.379355524466769</v>
       </c>
       <c r="C3" t="n">
-        <v>27.03242303643592</v>
+        <v>14.07826207889926</v>
       </c>
       <c r="D3" t="n">
-        <v>83.954154928666</v>
+        <v>42.29859983747383</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.65675782307466</v>
+        <v>6.011241193103221</v>
       </c>
       <c r="C4" t="n">
-        <v>81.00498482510856</v>
+        <v>55.65822259686442</v>
       </c>
       <c r="D4" t="n">
-        <v>178.4355904899705</v>
+        <v>114.0987181875643</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>70.31767931667781</v>
+        <v>11.90369091399258</v>
       </c>
       <c r="C5" t="n">
-        <v>190.5326857016997</v>
+        <v>167.7070515779614</v>
       </c>
       <c r="D5" t="n">
-        <v>170.6522946907018</v>
+        <v>128.2653375598458</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>61.58503348740243</v>
+        <v>10.6666888066416</v>
       </c>
       <c r="C6" t="n">
-        <v>266.8684784454105</v>
+        <v>324.0660814425339</v>
       </c>
       <c r="D6" t="n">
-        <v>95.75868932452966</v>
+        <v>84.48822567977626</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.72076704583318</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C7" t="n">
-        <v>242.061677454502</v>
+        <v>329.0769217250096</v>
       </c>
       <c r="D7" t="n">
-        <v>47.90928796724435</v>
+        <v>43.23813239043802</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>1.752419652080557</v>
       </c>
       <c r="C8" t="n">
-        <v>155.5481062608646</v>
+        <v>168.1488380448724</v>
       </c>
       <c r="D8" t="n">
-        <v>34.63115026730623</v>
+        <v>28.87319998189869</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>58.79687000734145</v>
+        <v>58.02030757328223</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>22.63124807829746</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>20.4988920646734</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>15.99267010218054</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>17.76963344686726</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>12.80100831567416</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.848451000647497</v>
+        <v>0.2002765316663493</v>
       </c>
       <c r="C2" t="n">
-        <v>11.22235800724529</v>
+        <v>11.74661128131308</v>
       </c>
       <c r="D2" t="n">
-        <v>12.87758463660541</v>
+        <v>8.093528073810704</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.61684065790326</v>
+        <v>1.055378782065321</v>
       </c>
       <c r="C3" t="n">
-        <v>23.25269437508571</v>
+        <v>30.10038461220721</v>
       </c>
       <c r="D3" t="n">
-        <v>76.07562960208534</v>
+        <v>40.05530633326987</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.27539774547039</v>
+        <v>4.35208757292611</v>
       </c>
       <c r="C4" t="n">
-        <v>74.11311594129596</v>
+        <v>45.16726662928301</v>
       </c>
       <c r="D4" t="n">
-        <v>178.7418957736955</v>
+        <v>108.8532402037736</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>69.60591223109887</v>
+        <v>10.62741889847172</v>
       </c>
       <c r="C5" t="n">
-        <v>172.542159021377</v>
+        <v>135.6775327269092</v>
       </c>
       <c r="D5" t="n">
-        <v>188.6428213710246</v>
+        <v>139.2363681548039</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>72.93600044390405</v>
+        <v>13.24279478258523</v>
       </c>
       <c r="C6" t="n">
-        <v>284.7402136535194</v>
+        <v>298.7477898977129</v>
       </c>
       <c r="D6" t="n">
-        <v>117.494583496554</v>
+        <v>102.6819741348782</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.0279973240002</v>
+        <v>8.444012004226815</v>
       </c>
       <c r="C7" t="n">
-        <v>298.1155443761779</v>
+        <v>393.215480991158</v>
       </c>
       <c r="D7" t="n">
-        <v>58.50921792999716</v>
+        <v>54.43692845278139</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.51451791248334</v>
+        <v>3.337942194439155</v>
       </c>
       <c r="C8" t="n">
-        <v>217.8007281871549</v>
+        <v>293.2382217814798</v>
       </c>
       <c r="D8" t="n">
-        <v>37.71874679716245</v>
+        <v>33.12907627980861</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.773437264497239</v>
+        <v>0.9984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>107.1656159001733</v>
+        <v>126.0249892987545</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>24.51718541815559</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>43.98720588877834</v>
+        <v>44.27191272300992</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>21.06830573313655</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>21.50125647070939</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>18.48041878474196</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>14.97067074205961</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>14.53673825678252</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>7.883434065101886</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.27884171020187</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.299294181075035</v>
+        <v>2.945243112740431</v>
       </c>
       <c r="C2" t="n">
-        <v>2.447497026687298</v>
+        <v>15.99659709299753</v>
       </c>
       <c r="D2" t="n">
-        <v>16.12913303307085</v>
+        <v>12.39849175693297</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.787181732356694</v>
+        <v>0.6234097921967245</v>
       </c>
       <c r="C2" t="n">
-        <v>6.463826884761</v>
+        <v>28.8879261974624</v>
       </c>
       <c r="D2" t="n">
-        <v>9.580875845744622</v>
+        <v>10.02855279888117</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.90707812546182</v>
+        <v>0.859029241215959</v>
       </c>
       <c r="C3" t="n">
-        <v>32.65783738177014</v>
+        <v>37.21314672947535</v>
       </c>
       <c r="D3" t="n">
-        <v>81.25434874198726</v>
+        <v>37.47821860962198</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>52.99081408442584</v>
+        <v>3.216205479112551</v>
       </c>
       <c r="C4" t="n">
-        <v>105.3690176014017</v>
+        <v>58.83613991551135</v>
       </c>
       <c r="D4" t="n">
-        <v>183.119508786932</v>
+        <v>104.8202206347277</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.36241343824987</v>
+        <v>9.007535186464487</v>
       </c>
       <c r="C5" t="n">
-        <v>248.799411948748</v>
+        <v>110.9129468872834</v>
       </c>
       <c r="D5" t="n">
-        <v>170.9222753093697</v>
+        <v>145.0777669950724</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.58747034223387</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="C6" t="n">
-        <v>249.3590081401686</v>
+        <v>264.5741340605857</v>
       </c>
       <c r="D6" t="n">
-        <v>91.08949724313183</v>
+        <v>117.2128219054352</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.94684675525043</v>
+        <v>11.43834250217959</v>
       </c>
       <c r="C7" t="n">
-        <v>153.1300616653047</v>
+        <v>409.7441853398573</v>
       </c>
       <c r="D7" t="n">
-        <v>33.95570784678443</v>
+        <v>67.37243620393737</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.919316761802514</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>78.94233289848603</v>
+        <v>392.8757962854885</v>
       </c>
       <c r="D8" t="n">
-        <v>24.53387512912779</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>33.50312215512664</v>
+        <v>224.2046684619568</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>26.73593522975338</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>85.12734343524093</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>21.78007281871549</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.99267010218054</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>19.19120412261664</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>10.75013736150257</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.976700097005335</v>
+        <v>3.116067213279376</v>
       </c>
       <c r="C2" t="n">
-        <v>7.671376560984576</v>
+        <v>12.6508009169244</v>
       </c>
       <c r="D2" t="n">
-        <v>24.39053996430776</v>
+        <v>21.46002306713103</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.50179625005713</v>
+        <v>4.76147636559703</v>
       </c>
       <c r="C3" t="n">
-        <v>6.165375582669969</v>
+        <v>31.58282364561989</v>
       </c>
       <c r="D3" t="n">
-        <v>16.68480223367454</v>
+        <v>11.47172192412398</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39755998938874</v>
+        <v>11.67717522120719</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14016700327043</v>
+        <v>59.9428328021969</v>
       </c>
       <c r="D21" t="n">
-        <v>1.57618352816338</v>
+        <v>0.7784783480804792</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.21446296788231</v>
+        <v>1.991966091916778</v>
       </c>
       <c r="C2" t="n">
-        <v>5.486006171331176</v>
+        <v>5.640140560897926</v>
       </c>
       <c r="D2" t="n">
-        <v>30.163216465279</v>
+        <v>23.63950297055895</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.74218556887736</v>
+        <v>8.595201150680825</v>
       </c>
       <c r="C3" t="n">
-        <v>21.02412708644545</v>
+        <v>43.29998249580557</v>
       </c>
       <c r="D3" t="n">
-        <v>33.13889375685108</v>
+        <v>27.47420950334699</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>17.9443845382232</v>
+        <v>6.062292073724055</v>
       </c>
       <c r="C4" t="n">
-        <v>9.967684441217866</v>
+        <v>51.06364334098934</v>
       </c>
       <c r="D4" t="n">
-        <v>23.81523580961913</v>
+        <v>20.29272504678157</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.473243451175969</v>
+        <v>5.129631754689585</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43882727734837</v>
+        <v>13.6248928574203</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13240481046988</v>
+        <v>73.73471428721571</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250279426810184</v>
+        <v>1.602928571461211</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.139449231732052</v>
+        <v>1.368556299720054</v>
       </c>
       <c r="C2" t="n">
-        <v>7.200137662946108</v>
+        <v>7.019496085364694</v>
       </c>
       <c r="D2" t="n">
-        <v>29.09409321535422</v>
+        <v>27.96017461694916</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.05987091442583</v>
+        <v>7.647814616082653</v>
       </c>
       <c r="C3" t="n">
-        <v>21.22047662729481</v>
+        <v>30.19855938263188</v>
       </c>
       <c r="D3" t="n">
-        <v>49.57825906446393</v>
+        <v>40.69344234103029</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.78742807873073</v>
+        <v>12.34155039008665</v>
       </c>
       <c r="C4" t="n">
-        <v>35.07195498651306</v>
+        <v>86.02073384610553</v>
       </c>
       <c r="D4" t="n">
-        <v>35.05919226635785</v>
+        <v>29.97962964458485</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>15.33980787885642</v>
+        <v>6.037748381117885</v>
       </c>
       <c r="C5" t="n">
-        <v>12.83635123302705</v>
+        <v>57.67767762450012</v>
       </c>
       <c r="D5" t="n">
-        <v>31.19503330244241</v>
+        <v>27.4889357189107</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>10.58618549489336</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>31.55729820530948</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>24.13430381349934</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.42692138262712</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.699389580518</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.95717262057418</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72934434976387</v>
+        <v>14.82879724589867</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0490005335596</v>
+        <v>87.32513933695884</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182336087440967</v>
+        <v>2.471466207649779</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.133378819057324</v>
+        <v>1.432369900496096</v>
       </c>
       <c r="C2" t="n">
-        <v>6.450082416901544</v>
+        <v>8.688467182584272</v>
       </c>
       <c r="D2" t="n">
-        <v>21.96464138711389</v>
+        <v>26.14786835490955</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.6055016538088</v>
+        <v>6.013204688511713</v>
       </c>
       <c r="C3" t="n">
-        <v>25.08856258202724</v>
+        <v>28.46086594611503</v>
       </c>
       <c r="D3" t="n">
-        <v>60.66219064541041</v>
+        <v>53.61815086743955</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.8414652601933</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="C4" t="n">
-        <v>45.14174118897259</v>
+        <v>80.04778081346792</v>
       </c>
       <c r="D4" t="n">
-        <v>51.10193150145498</v>
+        <v>43.62297749050277</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.25041208450773</v>
+        <v>12.56637061435918</v>
       </c>
       <c r="C5" t="n">
-        <v>40.86524818927349</v>
+        <v>114.3981512373596</v>
       </c>
       <c r="D5" t="n">
-        <v>36.20194659410114</v>
+        <v>32.15223731408305</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.16229147083699</v>
+        <v>6.480516595733197</v>
       </c>
       <c r="C6" t="n">
-        <v>16.38242394076653</v>
+        <v>53.97747052719389</v>
       </c>
       <c r="D6" t="n">
-        <v>38.56108632740622</v>
+        <v>33.12711278440013</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.13997331554657</v>
+        <v>17.48689010804419</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.62700229231099</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>27.5124976638126</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>36.72030938194344</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.4902616239802</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>42.95931604243193</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.44199175555609</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05121714972874</v>
+        <v>16.05973322131923</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7627023577542</v>
+        <v>100.5846449124731</v>
       </c>
       <c r="D21" t="n">
-        <v>6.017072383242914</v>
+        <v>3.380996467646155</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.859872120199964</v>
+        <v>1.508946221427348</v>
       </c>
       <c r="C2" t="n">
-        <v>5.506622873120359</v>
+        <v>11.8055161435679</v>
       </c>
       <c r="D2" t="n">
-        <v>32.30440820824129</v>
+        <v>22.05398042820035</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.87548227247668</v>
+        <v>5.394703634836223</v>
       </c>
       <c r="C3" t="n">
-        <v>23.54721868635975</v>
+        <v>31.40610905885546</v>
       </c>
       <c r="D3" t="n">
-        <v>60.08786823842603</v>
+        <v>62.07590733952582</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.40156017323272</v>
+        <v>12.52022847225957</v>
       </c>
       <c r="C4" t="n">
-        <v>46.04789431999239</v>
+        <v>75.18518443433348</v>
       </c>
       <c r="D4" t="n">
-        <v>60.20175097211866</v>
+        <v>58.42773287054467</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.51347941151687</v>
+        <v>16.5915362017711</v>
       </c>
       <c r="C5" t="n">
-        <v>47.02571503342222</v>
+        <v>132.1186972990145</v>
       </c>
       <c r="D5" t="n">
-        <v>36.81553890925539</v>
+        <v>40.10439371848221</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.41638419978766</v>
+        <v>11.5119735799981</v>
       </c>
       <c r="C6" t="n">
-        <v>28.17615911188346</v>
+        <v>118.8228881404</v>
       </c>
       <c r="D6" t="n">
-        <v>32.04031807579891</v>
+        <v>35.54221213684728</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.108434215823654</v>
+        <v>7.246279805045708</v>
       </c>
       <c r="C7" t="n">
-        <v>14.55244622005047</v>
+        <v>47.60985491744906</v>
       </c>
       <c r="D7" t="n">
-        <v>30.84160412891355</v>
+        <v>36.9500383447372</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>24.70077223884975</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>30.39687241888974</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>30.56376952861169</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>45.84565429291754</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>5.858088551240717</v>
       </c>
       <c r="C12" t="n">
-        <v>19.52696183746906</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.40659208494097</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>31.03304493124168</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.054004588592273</v>
+        <v>17.31161481804056</v>
       </c>
       <c r="C21" t="n">
-        <v>66.13129301805256</v>
+        <v>113.3910770581657</v>
       </c>
       <c r="D21" t="n">
-        <v>4.40875286787017</v>
+        <v>4.327903704510141</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.510950774564847</v>
+        <v>1.959568417676633</v>
       </c>
       <c r="C2" t="n">
-        <v>5.585162689460105</v>
+        <v>16.0044510746315</v>
       </c>
       <c r="D2" t="n">
-        <v>28.4245412810579</v>
+        <v>23.33712467765093</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.47497026687298</v>
+        <v>5.198354093986861</v>
       </c>
       <c r="C3" t="n">
-        <v>22.23658550119026</v>
+        <v>38.85266539556753</v>
       </c>
       <c r="D3" t="n">
-        <v>72.70332623799754</v>
+        <v>64.45664552232434</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.33171721751096</v>
+        <v>11.30777005751476</v>
       </c>
       <c r="C4" t="n">
-        <v>54.2670860999467</v>
+        <v>76.78052445373456</v>
       </c>
       <c r="D4" t="n">
-        <v>77.15064333823558</v>
+        <v>72.88789480639595</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.85833489761475</v>
+        <v>17.7450897542611</v>
       </c>
       <c r="C5" t="n">
-        <v>70.34222300928397</v>
+        <v>135.211202567392</v>
       </c>
       <c r="D5" t="n">
-        <v>51.5908418581699</v>
+        <v>50.65818153913543</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.81389420901639</v>
+        <v>16.38242394076653</v>
       </c>
       <c r="C6" t="n">
-        <v>55.54728510628455</v>
+        <v>160.6443585936099</v>
       </c>
       <c r="D6" t="n">
-        <v>36.99127174831558</v>
+        <v>39.32586778901449</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.1750541909922</v>
+        <v>10.18072369303942</v>
       </c>
       <c r="C7" t="n">
-        <v>29.8235317596096</v>
+        <v>105.819639797651</v>
       </c>
       <c r="D7" t="n">
-        <v>33.35684174719388</v>
+        <v>39.04606969330414</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.091744504851458</v>
+        <v>8.011061266653972</v>
       </c>
       <c r="C8" t="n">
-        <v>19.19316761802514</v>
+        <v>42.39186586937727</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>39.05392367493811</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>31.39530983410874</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>38.38437174064178</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>34.02246669067321</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>46.02335062738621</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>44.91201222617883</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.66675522656638</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>31.03304493124168</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.274586704205594</v>
+        <v>17.69311077660747</v>
       </c>
       <c r="C21" t="n">
-        <v>75.47383705613304</v>
+        <v>126.5057420527434</v>
       </c>
       <c r="D21" t="n">
-        <v>5.455940028154195</v>
+        <v>5.30793323298224</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.639158813193679</v>
+        <v>1.753401399784803</v>
       </c>
       <c r="C2" t="n">
-        <v>4.378594760940774</v>
+        <v>10.24257379840697</v>
       </c>
       <c r="D2" t="n">
-        <v>26.778150381036</v>
+        <v>18.66695084854885</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.39504779220149</v>
+        <v>7.201119410650354</v>
       </c>
       <c r="C3" t="n">
-        <v>21.93224371287374</v>
+        <v>60.58855956759191</v>
       </c>
       <c r="D3" t="n">
-        <v>78.57417750939346</v>
+        <v>69.95934140462771</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.06592563156733</v>
+        <v>8.525497063679301</v>
       </c>
       <c r="C4" t="n">
-        <v>55.14771379065608</v>
+        <v>113.9328028255466</v>
       </c>
       <c r="D4" t="n">
-        <v>96.28196085089319</v>
+        <v>66.67245009080939</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.32590884674349</v>
+        <v>9.22842841992002</v>
       </c>
       <c r="C5" t="n">
-        <v>87.47372044839082</v>
+        <v>95.9903817827319</v>
       </c>
       <c r="D5" t="n">
-        <v>67.17608666308801</v>
+        <v>38.06726723217008</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.36611944488861</v>
+        <v>6.31950997223672</v>
       </c>
       <c r="C6" t="n">
-        <v>86.46055681760812</v>
+        <v>69.6756163181004</v>
       </c>
       <c r="D6" t="n">
-        <v>45.12210623488766</v>
+        <v>25.68055644768807</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.71509754378595</v>
+        <v>5.270021676396877</v>
       </c>
       <c r="C7" t="n">
-        <v>56.95216607106171</v>
+        <v>29.76364514965055</v>
       </c>
       <c r="D7" t="n">
-        <v>36.83026512481909</v>
+        <v>27.42806736124739</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.59796646734432</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>30.54217107911827</v>
+        <v>23.11524969649115</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>28.28906009787184</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>24.29531043699581</v>
+        <v>25.95937279569415</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>33.72499713628642</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>26.05067533218912</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>36.01541453029424</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
         <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.25041208450772</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>24.79894700927443</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>30.17205219461722</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>26.44435616159209</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>96.16709636949629</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.482591759918953</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>84.17915729908822</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.547267789929084</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
